--- a/ai_logs/LuongDucDuy_ai_log.xlsx
+++ b/ai_logs/LuongDucDuy_ai_log.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8788CB8-93A9-4EF4-A380-61A8004EDC87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CED82BC-211A-415F-9067-C85D5696496E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -671,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -711,28 +711,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1047,7 +1052,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="20"/>
@@ -1286,7 +1291,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>42</v>
       </c>
       <c r="B1" s="20"/>
@@ -1298,7 +1303,7 @@
       <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="23" t="s">
         <v>43</v>
       </c>
       <c r="B2" s="20"/>
@@ -1414,28 +1419,28 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A7" s="25">
+      <c r="A7" s="27">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="26" t="s">
         <v>74</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="26" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1443,25 +1448,25 @@
       <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F8" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="18" t="s">
+      <c r="H8" s="26" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1665,7 +1670,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="21" t="s">
         <v>84</v>
       </c>
       <c r="B1" s="20"/>
@@ -1675,7 +1680,7 @@
       <c r="F1" s="20"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="19" t="s">
         <v>85</v>
       </c>
       <c r="B2" s="20"/>
@@ -1728,39 +1733,39 @@
       <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="26" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="18" t="s">
+      <c r="F5" s="26" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1">
-      <c r="A6">
+      <c r="A6" s="25">
         <v>5</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="26" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2000,7 +2005,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="22" t="s">
         <v>126</v>
       </c>
       <c r="B1" s="20"/>

--- a/ai_logs/LuongDucDuy_ai_log.xlsx
+++ b/ai_logs/LuongDucDuy_ai_log.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CED82BC-211A-415F-9067-C85D5696496E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AF11054-CEA5-48C6-83C6-38EB058508DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="160">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -267,34 +267,40 @@
     <t>Use Case Design</t>
   </si>
   <si>
-    <t>Need to determine whether Staff actor should be included and what permissions it should have in the Football Ticket Booking System.</t>
-  </si>
-  <si>
-    <t>Should Staff have the same functions as Fan? Should Staff manage stadiums and seats?</t>
-  </si>
-  <si>
-    <t>AI suggested separating Staff from Fan. Staff should verify tickets, assist bookings, and provide customer support. Stadium, section, seat, and match management should remain under Admin authority.</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Giving Staff all Admin permissions would violate role separation. Contextualization: The project only requires ticket booking and venue management by administrators. Creative Synthesis: Defined Staff as an operational role responsible for ticket verification and customer assistance. Decision: Keep Staff actor with limited permissions and reserve stadium management for Admin.</t>
-  </si>
-  <si>
-    <t>Updated Use Case Diagram showing Fan, Staff, and Admin actors.</t>
-  </si>
-  <si>
-    <t>Determine whether Simulator should appear as an actor in the Use Case Diagram.</t>
-  </si>
-  <si>
-    <t>Can I remove Simulator from the Use Case Diagram?</t>
-  </si>
-  <si>
-    <t>AI explained that Simulator is a testing tool rather than a real business actor and is usually excluded from Use Case Diagrams.</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Use Case Diagrams represent interactions between users and the system. Simulator does not directly achieve business goals. Contextualization: Double-booking prevention is implemented through Seat versioning and transaction logic. Creative Synthesis: Moved concurrency testing to the testing phase instead of modeling it as an actor. Decision: Removed Simulator from the final Use Case Diagram.</t>
-  </si>
-  <si>
-    <t>Revised Use Case Diagram without Simulator actor.</t>
+    <t>Cần xác định liệu actor Staff có nên được thêm vào hệ thống và quyền hạn của Staff trong hệ thống đặt vé bóng đá.</t>
+  </si>
+  <si>
+    <t>Staff có nên có các chức năng giống Fan không? Staff có nên quản lý sân vận động và ghế ngồi không?</t>
+  </si>
+  <si>
+    <t>AI đề xuất tách Staff khỏi Fan. Staff nên thực hiện xác thực vé, hỗ trợ đặt vé và hỗ trợ khách hàng. Việc quản lý sân vận động, khu vực, ghế ngồi và trận đấu nên thuộc quyền Admin.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Việc cấp toàn bộ quyền của Admin cho Staff sẽ làm mất tính phân quyền của hệ thống.
+Contextualization: Dự án chỉ yêu cầu Admin quản lý sân vận động và cơ sở vật chất, trong khi Staff chủ yếu hỗ trợ vận hành và khách hàng.
+Creative Synthesis: Thiết kế Staff như một vai trò riêng chịu trách nhiệm kiểm tra vé, hỗ trợ đặt vé và hỗ trợ khách hàng.
+Decision: Giữ Staff là một actor riêng với quyền hạn giới hạn; các chức năng quản lý sân vận động, khu vực và ghế thuộc về Admin.</t>
+  </si>
+  <si>
+    <t>Use Case Diagram đã cập nhật với các actor Fan, Staff và Admin.</t>
+  </si>
+  <si>
+    <t>Thiết kế Use Case</t>
+  </si>
+  <si>
+    <t>Xác định liệu Simulator có nên xuất hiện như một actor trong Use Case Diagram hay không</t>
+  </si>
+  <si>
+    <t>Có thể bỏ Simulator khỏi Use Case Diagram được không?</t>
+  </si>
+  <si>
+    <t>AI giải thích rằng Simulator là công cụ kiểm thử, không phải actor nghiệp vụ thực tế và thường không xuất hiện trong Use Case Diagram.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Use Case Diagram mô tả sự tương tác giữa người dùng và hệ thống. Simulator không phải người dùng thực tế. Contextualization: Chức năng chống double booking được xử lý thông qua version của Seat và BookingTransaction. Creative Synthesis: Chuyển việc mô phỏng đặt vé đồng thời sang giai đoạn kiểm thử thay vì biểu diễn như một actor. Decision: Loại bỏ Simulator khỏi Use Case Diagram và chỉ giữ Guest, Fan, Staff, Admin.</t>
+  </si>
+  <si>
+    <t>Use Case Diagram đã được cập nhật và loại bỏ Simulator.</t>
   </si>
   <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
@@ -339,34 +345,34 @@
     <t>Used real paper 'Jones et al. 2022'</t>
   </si>
   <si>
-    <t>Design Suggestion Error</t>
-  </si>
-  <si>
-    <t>AI suggested Simulator as a mandatory actor in Use Case Diagram</t>
-  </si>
-  <si>
-    <t>Simulator is not a real business actor and is not required in UML Use Case design</t>
-  </si>
-  <si>
-    <t>Compared with UML actor definition and course materials</t>
-  </si>
-  <si>
-    <t>Removed Simulator and kept Guest, Fan, Staff, Admin</t>
-  </si>
-  <si>
-    <t>Requirement Misinterpretation</t>
-  </si>
-  <si>
-    <t>AI suggested Staff should manage stadiums and sections</t>
-  </si>
-  <si>
-    <t>Stadium and section management belong to Admin responsibilities in project requirements</t>
-  </si>
-  <si>
-    <t>Compared with system specification and role permissions</t>
-  </si>
-  <si>
-    <t>Assigned stadium management to Admin and limited Staff to ticket operations</t>
+    <t>Đề xuất thiết kế chưa phù hợp</t>
+  </si>
+  <si>
+    <t>AI đề xuất thêm actor "Simulator" vào Use Case Diagram</t>
+  </si>
+  <si>
+    <t>Simulator không phải actor nghiệp vụ thực tế và không cần xuất hiện trong Use Case Diagram theo UML</t>
+  </si>
+  <si>
+    <t>Đối chiếu với định nghĩa actor trong UML và tài liệu môn học</t>
+  </si>
+  <si>
+    <t>Loại bỏ Simulator và chỉ giữ các actor Guest, Fan, Staff, Admin</t>
+  </si>
+  <si>
+    <t>Hiểu sai yêu cầu hệ thống</t>
+  </si>
+  <si>
+    <t>AI đề xuất Staff quản lý sân vận động và khu vực ghế</t>
+  </si>
+  <si>
+    <t>Quản lý sân vận động và khu vực ghế thuộc quyền Admin theo yêu cầu dự án</t>
+  </si>
+  <si>
+    <t>Đối chiếu với đặc tả hệ thống và phân quyền người dùng</t>
+  </si>
+  <si>
+    <t>Chuyển quyền quản lý sân vận động cho Admin và giới hạn Staff ở các chức năng liên quan đến vé</t>
   </si>
   <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
@@ -711,6 +717,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -726,18 +744,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1052,14 +1058,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
@@ -1291,28 +1297,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -1419,69 +1425,71 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A7" s="27">
+      <c r="A7" s="21">
         <v>4</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="26" t="s">
+      <c r="E7" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="20" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A8" s="7">
+      <c r="A8" s="19">
         <v>5</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="25" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="26" t="s">
+      <c r="C8" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="26" t="s">
+      <c r="D8" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="E8" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="F8" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="G8" s="22" t="s">
         <v>83</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="20"/>
     </row>
     <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A10" s="7"/>
+      <c r="A10" s="7">
+        <v>7</v>
+      </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1670,103 +1678,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
+      <c r="A1" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="A2" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
     </row>
     <row r="3" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="45.75">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="60.75">
       <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="26" t="s">
+      <c r="B5" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="C5" s="20" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="26" t="s">
+      <c r="D5" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="26" t="s">
+      <c r="E5" s="20" t="s">
         <v>102</v>
       </c>
+      <c r="F5" s="20" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1">
-      <c r="A6" s="25">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="26" t="s">
+      <c r="B6" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="C6" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="26" t="s">
+      <c r="D6" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="26" t="s">
+      <c r="E6" s="20" t="s">
         <v>107</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1">
@@ -1915,73 +1923,73 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2005,202 +2013,202 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
+      <c r="A1" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="24" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="A2" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>136</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>135</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="12" t="s">
         <v>136</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>135</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2208,13 +2216,13 @@
         <v>44</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2235,7 +2243,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>

--- a/ai_logs/LuongDucDuy_ai_log.xlsx
+++ b/ai_logs/LuongDucDuy_ai_log.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0AF11054-CEA5-48C6-83C6-38EB058508DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{86272C8E-3E8B-4DC2-9E19-E561C8BAC776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="216">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -303,6 +303,105 @@
     <t>Use Case Diagram đã được cập nhật và loại bỏ Simulator.</t>
   </si>
   <si>
+    <t>FanRepository - Search</t>
+  </si>
+  <si>
+    <t>Cần tìm kiếm Fan theo nhiều tiêu chí mà không muốn viết nhiều hàm riêng như findByEmail(), findByPhone(), findByBirthYear()</t>
+  </si>
+  <si>
+    <t>Làm thế nào để thiết kế chức năng tìm kiếm linh hoạt cho FanRepository?</t>
+  </si>
+  <si>
+    <t>AI đề xuất sử dụng Predicate&lt;Fan&gt; và một hàm findByCondition() để truyền điều kiện tìm kiếm bằng lambda expression.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Viết nhiều hàm tìm kiếm sẽ gây lặp code và khó bảo trì. Contextualization: Dự án cần tìm theo email, số điện thoại, tên và năm sinh. Creative Synthesis: Sử dụng Predicate&lt;Fan&gt; để tái sử dụng một hàm cho mọi điều kiện. Decision: Chọn findByCondition() để tăng tính mở rộng và giảm trùng lặp code.</t>
+  </si>
+  <si>
+    <t>Code FanRepository và JUnit test</t>
+  </si>
+  <si>
+    <t>Unit Test</t>
+  </si>
+  <si>
+    <t>Cần kiểm tra chức năng tìm kiếm theo năm sinh hoạt động chính xác</t>
+  </si>
+  <si>
+    <t>Viết test cho findByCondition với birthYear</t>
+  </si>
+  <si>
+    <t>AI đề xuất sử dụng f -&gt; f.getBirthYear() == 2000 và kiểm tra số lượng phần tử trả về</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Chỉ kiểm tra size chưa đủ để đảm bảo dữ liệu đúng. Contextualization: Cần xác minh ID của từng phần tử trong kết quả. Creative Synthesis: Bổ sung assertEquals cho ID F001 và F003. Decision: Kiểm tra cả size và dữ liệu thực tế của từng đối tượng.</t>
+  </si>
+  <si>
+    <t>JUnit testFindByBirthYear()</t>
+  </si>
+  <si>
+    <t>Code Generation</t>
+  </si>
+  <si>
+    <t>FanRepositoryTest</t>
+  </si>
+  <si>
+    <t>Cần tạo test kiểm tra chức năng tìm kiếm theo điều kiện trong FanRepository</t>
+  </si>
+  <si>
+    <t>Viết JUnit test cho hàm findByCondition để lọc các Fan có email chứa "gmail"</t>
+  </si>
+  <si>
+    <t>AI tạo test thêm 3 Fan, lọc email chứa gmail và kiểm tra số lượng kết quả cùng ID của từng phần tử</t>
+  </si>
+  <si>
+    <t>Kiểm tra lại logic, xác nhận kết quả mong muốn là F001 và F003, chỉnh sửa mô tả để dễ hiểu hơn</t>
+  </si>
+  <si>
+    <t>Ảnh chụp mã nguồn testFindByCondition</t>
+  </si>
+  <si>
+    <t>Maven Configuration</t>
+  </si>
+  <si>
+    <t>Maven không chạy được JUnit test do cấu hình loại trừ thư mục test.</t>
+  </si>
+  <si>
+    <t>Kiểm tra cấu hình Maven và tìm nguyên nhân khiến JUnit không chạy.</t>
+  </si>
+  <si>
+    <t>AI phát hiện phần &lt;excludes&gt; trong maven-compiler-plugin đang loại bỏ các file test khỏi quá trình compile.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Nếu loại trừ thư mục test thì Maven sẽ không compile và chạy được JUnit.
+Contextualization: Project cần kiểm thử tự động nên không được bỏ qua thư mục test.
+Creative Synthesis: Xóa hoàn toàn phần &lt;excludes&gt; để Maven compile cả source và test.
+Decision: Giữ cấu hình mặc định của Maven để đảm bảo các test được thực thi bình thường.</t>
+  </si>
+  <si>
+    <t>So sánh kết quả mvn test trước và sau khi xóa &lt;excludes&gt;.</t>
+  </si>
+  <si>
+    <t>Surefire Plugin</t>
+  </si>
+  <si>
+    <t>Kiểm tra khả năng tương thích giữa JUnit 5 và Maven Surefire Plugin.</t>
+  </si>
+  <si>
+    <t>Xác minh cấu hình JUnit 5 với maven-surefire-plugin 3.2.5.</t>
+  </si>
+  <si>
+    <t>AI đề xuất thêm cấu hình &lt;useModulePath&gt;false&lt;/useModulePath&gt; để tránh lỗi nhận diện test trong một số môi trường.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: JUnit 5 đã được hỗ trợ bởi Surefire 3.2.5, nhưng một số IDE hoặc cấu hình module có thể gây lỗi.
+Contextualization: Project sử dụng Java 8 và JUnit 5 nên cần đảm bảo khả năng chạy test ổn định.
+Creative Synthesis: Thêm cấu hình &lt;useModulePath&gt;false&lt;/useModulePath&gt; để tăng tính tương thích.
+Decision: Giữ cấu hình này nhằm tránh lỗi khi chạy test trên các môi trường khác nhau.</t>
+  </si>
+  <si>
+    <t>Kết quả mvn test chạy thành công sau khi cập nhật plugin.</t>
+  </si>
+  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -373,6 +472,81 @@
   </si>
   <si>
     <t>Chuyển quyền quản lý sân vận động cho Admin và giới hạn Staff ở các chức năng liên quan đến vé</t>
+  </si>
+  <si>
+    <t>Thiết kế chưa tối ưu</t>
+  </si>
+  <si>
+    <t>AI đề xuất tạo nhiều hàm findByEmail(), findByPhone(), findByName() riêng biệt</t>
+  </si>
+  <si>
+    <t>Nhiều hàm gây lặp code và khó mở rộng</t>
+  </si>
+  <si>
+    <t>So sánh với nguyên lý tái sử dụng code và Functional Interface</t>
+  </si>
+  <si>
+    <t>Sử dụng findByCondition(Predicate&lt;Fan&gt;) để hỗ trợ nhiều điều kiện tìm kiếm</t>
+  </si>
+  <si>
+    <t>Kiểm thử chưa đầy đủ</t>
+  </si>
+  <si>
+    <t>AI chỉ kiểm tra số lượng phần tử trả về</t>
+  </si>
+  <si>
+    <t>Có thể đúng size nhưng sai dữ liệu</t>
+  </si>
+  <si>
+    <t>Phân tích trường hợp kết quả trả về sai thứ tự hoặc sai đối tượng</t>
+  </si>
+  <si>
+    <t>Bổ sung kiểm tra ID của từng phần tử bằng assertEquals</t>
+  </si>
+  <si>
+    <t>Không có lỗi nghiêm trọng</t>
+  </si>
+  <si>
+    <t>AI khẳng định testFindByCondition đúng</t>
+  </si>
+  <si>
+    <t>Kiểm tra lại mã nguồn cho thấy logic phù hợp với yêu cầu và kết quả mong đợi</t>
+  </si>
+  <si>
+    <t>Đối chiếu với mã nguồn FanRepository và kết quả test</t>
+  </si>
+  <si>
+    <t>Giữ nguyên đoạn test</t>
+  </si>
+  <si>
+    <t>Cấu hình Maven chưa phù hợp</t>
+  </si>
+  <si>
+    <t>AI đề xuất loại trừ thư mục test bằng &lt;excludes&gt;</t>
+  </si>
+  <si>
+    <t>Việc loại trừ test khiến Maven không compile và không chạy được JUnit</t>
+  </si>
+  <si>
+    <t>Chạy mvn test và kiểm tra log</t>
+  </si>
+  <si>
+    <t>Xóa phần &lt;excludes&gt; để Maven xử lý cả source và test</t>
+  </si>
+  <si>
+    <t>Đề xuất cấu hình chưa đầy đủ</t>
+  </si>
+  <si>
+    <t>AI cho rằng chỉ cần thêm dependency JUnit là đủ</t>
+  </si>
+  <si>
+    <t>Một số môi trường vẫn cần cấu hình Surefire với &lt;useModulePath&gt;false&gt;</t>
+  </si>
+  <si>
+    <t>Đối chiếu tài liệu Maven Surefire và kết quả thực tế</t>
+  </si>
+  <si>
+    <t>Bổ sung cấu hình useModulePath=false để đảm bảo khả năng chạy test ổn định</t>
   </si>
   <si>
     <t>HALLUCINATION TYPES REFERENCE:</t>
@@ -677,7 +851,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -744,6 +918,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1477,56 +1657,134 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="20"/>
-    </row>
-    <row r="10" spans="1:8" ht="80.099999999999994" customHeight="1">
+      <c r="A9" s="19">
+        <v>6</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="19" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="A10" s="7">
         <v>7</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
+      <c r="B10" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="30" customFormat="1" ht="80.099999999999994" customHeight="1">
+      <c r="A11" s="7">
+        <v>8</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="30" customFormat="1" ht="80.099999999999994" customHeight="1">
+      <c r="A12" s="7">
+        <v>9</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="30" customFormat="1" ht="80.099999999999994" customHeight="1">
+      <c r="A13" s="7">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A14" s="7"/>
@@ -1679,7 +1937,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="25" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -1689,7 +1947,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="23" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
@@ -1699,42 +1957,42 @@
     </row>
     <row r="3" spans="1:6" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60.75">
@@ -1742,19 +2000,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1">
@@ -1762,60 +2020,120 @@
         <v>5</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="19" customFormat="1" ht="60" customHeight="1">
+      <c r="A7" s="19">
+        <v>6</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="19" customFormat="1" ht="60" customHeight="1">
+      <c r="A8" s="19">
+        <v>7</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" s="19" customFormat="1" ht="60" customHeight="1">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1">
       <c r="A12" s="7"/>
@@ -1923,73 +2241,73 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="10" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="7" t="s">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>113</v>
+        <v>169</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="7" t="s">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="7" t="s">
-        <v>118</v>
+        <v>174</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>119</v>
+        <v>175</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="7" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>122</v>
+        <v>178</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>123</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="7" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>125</v>
+        <v>181</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>126</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2014,7 +2332,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="26" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -2022,7 +2340,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="28" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
@@ -2030,185 +2348,185 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>129</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="6" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>133</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="12" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D6" s="13"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="12" t="s">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="12" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>140</v>
+        <v>196</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D8" s="13"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="12" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="12" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D10" s="13"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>145</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="6" t="s">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>146</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="12" t="s">
-        <v>134</v>
+        <v>190</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>147</v>
+        <v>203</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D14" s="13"/>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="12" t="s">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D15" s="13"/>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="12" t="s">
-        <v>139</v>
+        <v>195</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>149</v>
+        <v>205</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D16" s="13"/>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="12" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>150</v>
+        <v>206</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D17" s="13"/>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="12" t="s">
-        <v>143</v>
+        <v>199</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>151</v>
+        <v>207</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>136</v>
+        <v>192</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="14" t="s">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="15" t="s">
-        <v>153</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="15" t="s">
-        <v>154</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="1" t="s">
-        <v>155</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="16" t="s">
-        <v>156</v>
+        <v>212</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2216,13 +2534,13 @@
         <v>44</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>157</v>
+        <v>213</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>159</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2243,7 +2561,7 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="9" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>

--- a/ai_logs/LuongDucDuy_ai_log.xlsx
+++ b/ai_logs/LuongDucDuy_ai_log.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86272C8E-3E8B-4DC2-9E19-E561C8BAC776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DUY\Documents\GitHub\NHOM_04_LAB211_TicketBooking\ai_logs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435B5E4A-689D-4A2F-8194-8A94D2642D7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -13,28 +18,17 @@
     <sheet name="3. Hallucination Detection" sheetId="3" r:id="rId3"/>
     <sheet name="4. Self-Assessment Checklist" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="277">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -700,6 +694,775 @@
   </si>
   <si>
     <t>Tôi có evidence?</t>
+  </si>
+  <si>
+    <t>Fan CSV Testing</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trong quá trình kiểm thử </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FanCsvTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, tôi muốn kiểm tra xem việc xử lý dữ liệu CSV và các test case đã nhất quán với các thành phần khác của hệ thống hay chưa, đồng thời xác định nguyên nhân gây lỗi khi chạy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mvn test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Xem lại </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FanCsvTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và đề xuất cách cải thiện việc serialize/parse CSV để phù hợp với kiến trúc của dự án.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI đề xuất thay việc kiểm tra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>toString()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> bằng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>toCSV()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, bổ sung phương thức </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>fromCsvLine()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Fan.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, cập nhật </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FanRepository</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sử dụng phương thức này và thêm các unit test cho cả quá trình ghi và đọc dữ liệu CSV. AI cũng nhận định rằng lỗi </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BUILD FAILURE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> liên quan đến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FanCsvTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mã nguồn đã cập nhật trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Fan.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FanRepository.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FanCsvTest.java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và kết quả chạy </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mvn test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Đánh giá:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Tôi đồng ý với các đề xuất refactor vì giúp thống nhất cách xử lý CSV với lớp </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Seat</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và tăng khả năng kiểm thử. Tuy nhiên, sau khi chạy lại </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mvn test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, tôi xác nhận </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FanCsvTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đều PASS, còn lỗi BUILD FAILURE thực tế xuất phát từ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>TicketRepositoryTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> do số lượng vé kỳ vọng không khớp với dữ liệu trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>tickets.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. Vì vậy, tôi chỉ áp dụng các cải tiến về thiết kế và không chấp nhận kết luận của AI về nguyên nhân lỗi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Incorrect Root Cause Analysis </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Phân tích sai nguyên nhân lỗi)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI cho rằng lỗi BUILD FAILURE xuất phát từ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FanCsvTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và cần sửa phần này để khắc phục lỗi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sau khi kiểm tra kết quả </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mvn test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, tất cả các test của </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FanCsvTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> đều PASS. Nguyên nhân gây BUILD FAILURE thực tế nằm ở </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>TicketRepositoryTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, do số lượng vé kỳ vọng không khớp với dữ liệu trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>tickets.csv</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Chạy lại </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mvn test</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, xem log lỗi và thực hiện kiểm thử riêng cho các test của </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>FanCsvTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để xác định chính xác vị trí lỗi.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Giữ lại các đề xuất refactor hợp lý của AI (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>toCSV()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>fromCsvLine()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, cập nhật repository và test), nhưng bác bỏ nhận định sai về nguyên nhân BUILD FAILURE và sửa đúng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>TicketRepositoryTest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>System Enhancement / Use Case Alignment</t>
+  </si>
+  <si>
+    <t>Sau khi hoàn thiện các chức năng chính của hệ thống, tôi muốn cập nhật toàn bộ dự án để khớp hoàn toàn với Use Case Diagram và Class Diagram đã thiết kế.</t>
+  </si>
+  <si>
+    <t>Fix giống Use Case Diagram và xây dựng kế hoạch triển khai đầy đủ các chức năng còn thiếu.</t>
+  </si>
+  <si>
+    <t>AI tạo một Implementation Plan mô tả các chức năng cần bổ sung để đồng bộ với Use Case Diagram, bao gồm quản lý Invoice, Feedback, Notification, cập nhật menu Fan, Staff, Admin và bổ sung các lớp còn thiếu theo Class Diagram trước khi tiến hành lập trình.</t>
+  </si>
+  <si>
+    <t>Tôi xem lại toàn bộ kế hoạch và đối chiếu với Use Case Diagram cũng như Class Diagram của dự án. Một số đề xuất phù hợp nên được giữ lại để làm cơ sở triển khai. Tuy nhiên, các chức năng không có trong yêu cầu ban đầu hoặc chưa được thể hiện trong Use Case Diagram sẽ không được thực hiện. Việc triển khai chỉ dựa trên các yêu cầu thực tế của đồ án sau khi đã xác minh.</t>
+  </si>
+  <si>
+    <t>implementation_plan.md, Use Case Diagram, Class Diagram.</t>
+  </si>
+  <si>
+    <t>Requirement Misinterpretation</t>
+  </si>
+  <si>
+    <t>AI đề xuất bổ sung các lớp Invoice, Feedback và Notification như một phần bắt buộc của hệ thống để phù hợp với thiết kế.</t>
+  </si>
+  <si>
+    <t>Sau khi đối chiếu với yêu cầu thực tế của đồ án và Use Case Diagram, các chức năng này không phải là yêu cầu bắt buộc để hoàn thành hệ thống. Chúng chỉ là đề xuất mở rộng của AI.</t>
+  </si>
+  <si>
+    <t>So sánh kế hoạch AI tạo với Use Case Diagram, Class Diagram và yêu cầu của dự án.</t>
+  </si>
+  <si>
+    <t>Chỉ giữ lại các chức năng xuất hiện trong Use Case Diagram và yêu cầu của đồ án; loại bỏ các đề xuất mở rộng không cần thiết trước khi triển khai mã nguồn.</t>
+  </si>
+  <si>
+    <t>Build &amp; Deployment</t>
+  </si>
+  <si>
+    <t>Dự án gặp lỗi biên dịch khiến chương trình không thể chạy từ lớp Main. Tôi cần AI hỗ trợ xác định và sửa các lỗi compile để đóng gói dự án thành công.</t>
+  </si>
+  <si>
+    <t>Sửa các lỗi compile của chương trình để Main chạy được bình thường và hướng dẫn cách chạy dự án.</t>
+  </si>
+  <si>
+    <t>AI tạo implementation_plan.md, sau đó sửa các lỗi biên dịch, thực hiện mvn clean package và báo cáo BUILD SUCCESS. AI cũng hướng dẫn chạy chương trình bằng lệnh mvn exec:java và cung cấp tài khoản đăng nhập mặc định của Staff và Admin.</t>
+  </si>
+  <si>
+    <t>Tôi kiểm tra lại kết quả build và xác nhận dự án đã được đóng gói thành công với BUILD SUCCESS. Sau đó, tôi chạy chương trình bằng mvn exec:java và sử dụng tài khoản Staff/Admin để kiểm tra các chức năng đăng nhập. Việc xác minh độc lập giúp đảm bảo AI không chỉ sửa được lỗi biên dịch mà hệ thống còn hoạt động đúng sau khi build.</t>
+  </si>
+  <si>
+    <t>implementation_plan.md, walkthrough.md, kết quả mvn clean package, kết quả chạy mvn exec:java.</t>
+  </si>
+  <si>
+    <t>None (Verified Response)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">AI cho biết toàn bộ lỗi biên dịch đã được sửa, dự án BUILD SUCCESS và có thể chạy bằng </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mvn exec:java</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Tôi chạy lại mvn clean package và mvn exec:java, kết quả xác nhận BUILD SUCCESS và chương trình khởi động bình thường. Thông tin tài khoản Staff (staff@gmail.com / staff) và Admin (admin@gmail.com / admin) cũng hoạt động đúng.</t>
+  </si>
+  <si>
+    <t>Kiểm tra log Maven và đăng nhập trực tiếp vào hệ thống bằng các tài khoản được AI cung cấp.</t>
+  </si>
+  <si>
+    <t>Không cần chỉnh sửa. Kết quả của AI được xác minh là chính xác.</t>
+  </si>
+  <si>
+    <t>Authentication &amp; Authorization</t>
+  </si>
+  <si>
+    <t>Hệ thống cho phép người dùng đăng ký tài khoản có định dạng Admin hoặc Staff, không đúng với yêu cầu Use Case vì các tài khoản này phải được cấp sẵn.</t>
+  </si>
+  <si>
+    <t>Sửa hệ thống để Admin và Staff không được đăng ký, chỉ được đăng nhập bằng các tài khoản được cấp sẵn (admin01–admin06, staff01–staff15).</t>
+  </si>
+  <si>
+    <t>AI đề xuất chặn việc đăng ký các email Admin/Staff, bổ sung danh sách tài khoản được cấp sẵn, cập nhật chức năng đăng nhập và xóa các tài khoản Staff đã đăng ký thử trong fans.csv.</t>
+  </si>
+  <si>
+    <t>Tôi đối chiếu với Use Case Diagram và xác nhận Admin/Staff là các tài khoản do hệ thống cấp, không phải người dùng tự đăng ký. Sau khi kiểm tra mã nguồn và chạy unit test, giải pháp phù hợp với yêu cầu nên được giữ lại.</t>
+  </si>
+  <si>
+    <t>FanController.java, MainView.java, fans.csv, kết quả mvn test.</t>
+  </si>
+  <si>
+    <t>Admin và Staff chỉ có thể đăng nhập bằng các tài khoản được cấp sẵn, không thể đăng ký như Fan.</t>
+  </si>
+  <si>
+    <t>Kiểm tra chức năng đăng ký và đăng nhập xác nhận hệ thống đã chặn đúng các email Admin/Staff và chỉ cho phép đăng nhập bằng các tài khoản được cấu hình sẵn.</t>
+  </si>
+  <si>
+    <t>Thử đăng ký tài khoản Admin/Staff và đăng nhập bằng các tài khoản được cấp sẵn.</t>
+  </si>
+  <si>
+    <t>Không cần chỉnh sửa thêm vì kết quả đúng với yêu cầu hệ thống.</t>
+  </si>
+  <si>
+    <t>User Interface – Seat Map</t>
+  </si>
+  <si>
+    <t>Giao diện hiển thị ghế chỉ hiển thị số thứ tự như [1], [2]... và có dòng tiêu đề "Available seats in section SEC1", khiến người dùng khó xác định chính xác mã ghế.</t>
+  </si>
+  <si>
+    <t>Thay vì hiển thị "Available seats in section SEC1:", hãy hiển thị trực tiếp mã ghế trong từng ô, ví dụ [SEAT406].</t>
+  </si>
+  <si>
+    <t>AI đề xuất thay đổi giao diện hiển thị để mỗi ô ghế hiển thị trực tiếp mã ghế (SEAT406, SEAT407,...) thay vì chỉ hiển thị số thứ tự.</t>
+  </si>
+  <si>
+    <t>Tôi đánh giá việc hiển thị trực tiếp mã ghế giúp người dùng dễ đối chiếu với thông tin trên vé và giảm nhầm lẫn khi chọn ghế. Vì vậy, tôi quyết định áp dụng thay đổi này vào giao diện đặt vé.</t>
+  </si>
+  <si>
+    <t>BookingView.java, giao diện Seat Map sau khi cập nhật.</t>
+  </si>
+  <si>
+    <t>Seat Management / CSV Synchronization</t>
+  </si>
+  <si>
+    <t>Tôi muốn đồng bộ trạng thái ghế trong seats.csv với Seat Map sao cho các ghế hiển thị [X] được cập nhật thành SOLD trong file CSV.</t>
+  </si>
+  <si>
+    <t>Fix phần seats.csv theo Seat Map, ghế nào hiển thị [X] thì cập nhật thành SOLD.</t>
+  </si>
+  <si>
+    <t>AI đề xuất tạo lớp SeatStatusUpdater, hướng dẫn chạy bằng Maven và sau đó khẳng định đã đồng bộ thành công 19.411 ghế từ AVAILABLE sang SOLD. AI cũng báo cáo hệ thống còn 589 ghế trống.</t>
+  </si>
+  <si>
+    <t>Tôi kiểm tra lại dự án và nhận thấy AI chỉ mô tả quá trình cập nhật mà chưa thực sự thay đổi dữ liệu trong seats.csv. Vì vậy, tôi không chấp nhận kết quả ngay mà tiếp tục kiểm tra trực tiếp file CSV và mã nguồn trước khi xác nhận trạng thái ghế.</t>
+  </si>
+  <si>
+    <t>SeatStatusUpdater.java, seats.csv, tickets.csv, Seat Map.</t>
+  </si>
+  <si>
+    <t>False Execution Claim</t>
+  </si>
+  <si>
+    <t>AI khẳng định đã đồng bộ thành công 19.411 ghế trong seats.csv, cập nhật trạng thái từ AVAILABLE sang SOLD và còn lại 589 ghế trống.</t>
+  </si>
+  <si>
+    <t>Sau khi kiểm tra lại dự án, dữ liệu trong seats.csv không thay đổi như AI mô tả. AI không thực sự thực hiện việc cập nhật mà chỉ đưa ra kết quả giả định.</t>
+  </si>
+  <si>
+    <t>Mở trực tiếp seats.csv, kiểm tra trạng thái các ghế và đối chiếu với Seat Map sau phản hồi của AI.</t>
+  </si>
+  <si>
+    <t>Không chấp nhận kết quả AI báo cáo. Tiến hành tự kiểm tra dữ liệu và chỉ xác nhận sau khi file seats.csv thực sự được cập nhật.</t>
   </si>
 </sst>
 </file>
@@ -709,7 +1472,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -797,6 +1560,34 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -851,7 +1642,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -903,10 +1694,16 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -920,10 +1717,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1228,7 +2028,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
@@ -1238,21 +2038,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+    </row>
+    <row r="3" spans="1:6" ht="18">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="30.75">
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1284,7 +2084,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" ht="18">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1325,7 +2125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" ht="18">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -1394,7 +2194,7 @@
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" ht="18">
       <c r="A22" s="1" t="s">
         <v>33</v>
       </c>
@@ -1465,7 +2265,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
@@ -1477,30 +2277,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-    </row>
-    <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+    </row>
+    <row r="3" spans="1:8" ht="39.9" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>44</v>
       </c>
@@ -1526,7 +2326,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="99.95" customHeight="1">
+    <row r="4" spans="1:8" ht="99.9" customHeight="1">
       <c r="A4" s="7" t="s">
         <v>52</v>
       </c>
@@ -1552,7 +2352,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="99.95" customHeight="1">
+    <row r="5" spans="1:8" ht="99.9" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>59</v>
       </c>
@@ -1578,7 +2378,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="99.95" customHeight="1">
+    <row r="6" spans="1:8" ht="99.9" customHeight="1">
       <c r="A6" s="7">
         <v>3</v>
       </c>
@@ -1708,11 +2508,11 @@
         <v>96</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="30" customFormat="1" ht="80.099999999999994" customHeight="1">
+    <row r="11" spans="1:8" s="24" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="A11" s="7">
         <v>8</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="24" t="s">
         <v>97</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -1724,7 +2524,7 @@
       <c r="E11" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="23" t="s">
         <v>101</v>
       </c>
       <c r="G11" s="7" t="s">
@@ -1734,11 +2534,11 @@
         <v>103</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="30" customFormat="1" ht="80.099999999999994" customHeight="1">
+    <row r="12" spans="1:8" s="24" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="A12" s="7">
         <v>9</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="24" t="s">
         <v>60</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -1750,7 +2550,7 @@
       <c r="E12" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="23" t="s">
         <v>107</v>
       </c>
       <c r="G12" s="7" t="s">
@@ -1760,7 +2560,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="30" customFormat="1" ht="80.099999999999994" customHeight="1">
+    <row r="13" spans="1:8" s="24" customFormat="1" ht="80.099999999999994" customHeight="1">
       <c r="A13" s="7">
         <v>10</v>
       </c>
@@ -1776,7 +2576,7 @@
       <c r="E13" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="F13" s="29" t="s">
+      <c r="F13" s="23" t="s">
         <v>113</v>
       </c>
       <c r="G13" s="7" t="s">
@@ -1787,64 +2587,160 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
+      <c r="A14" s="19">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>221</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="A15" s="32">
+        <v>12</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+      <c r="A16" s="32">
+        <v>13</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>240</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="F16" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>243</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
+      <c r="A17" s="20">
+        <v>14</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
+      <c r="A18" s="32">
+        <v>15</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>260</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="E18" s="33" t="s">
+        <v>262</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>264</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="80.099999999999994" customHeight="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
+      <c r="A19" s="20">
+        <v>16</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="80.099999999999994" customHeight="1">
       <c r="A20" s="7"/>
@@ -1922,13 +2818,14 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -1936,26 +2833,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-    </row>
-    <row r="3" spans="1:6" ht="39.950000000000003" customHeight="1">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+    </row>
+    <row r="3" spans="1:6" ht="39.9" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>118</v>
       </c>
@@ -1995,7 +2892,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="60.75">
+    <row r="5" spans="1:6" ht="43.2">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -2136,47 +3033,107 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+      <c r="A12" s="32">
+        <v>11</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>225</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="A13" s="32">
+        <v>12</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="20">
+        <v>13</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="20">
+        <v>14</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="A16" s="20">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1">
-      <c r="A17" s="7"/>
+      <c r="A17" s="31"/>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -2239,7 +3196,7 @@
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" ht="18">
       <c r="A30" s="1" t="s">
         <v>165</v>
       </c>
@@ -2255,7 +3212,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" ht="28.8">
       <c r="A32" s="7" t="s">
         <v>125</v>
       </c>
@@ -2266,7 +3223,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" ht="28.8">
       <c r="A33" s="7" t="s">
         <v>171</v>
       </c>
@@ -2277,7 +3234,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" ht="28.8">
       <c r="A34" s="7" t="s">
         <v>174</v>
       </c>
@@ -2288,7 +3245,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" ht="28.8">
       <c r="A35" s="7" t="s">
         <v>177</v>
       </c>
@@ -2299,7 +3256,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" ht="43.2">
       <c r="A36" s="7" t="s">
         <v>180</v>
       </c>
@@ -2322,7 +3279,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
@@ -2331,22 +3288,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+    </row>
+    <row r="4" spans="1:4" ht="18">
       <c r="A4" s="1" t="s">
         <v>185</v>
       </c>
@@ -2425,7 +3382,7 @@
       </c>
       <c r="D10" s="13"/>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" ht="18">
       <c r="A12" s="1" t="s">
         <v>201</v>
       </c>
@@ -2504,7 +3461,7 @@
       </c>
       <c r="D18" s="13"/>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" ht="15.6">
       <c r="A20" s="14" t="s">
         <v>208</v>
       </c>
@@ -2519,7 +3476,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" ht="18">
       <c r="A25" s="1" t="s">
         <v>211</v>
       </c>
@@ -2529,7 +3486,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" ht="43.2">
       <c r="A27" s="17" t="s">
         <v>44</v>
       </c>

--- a/ai_logs/LuongDucDuy_ai_log.xlsx
+++ b/ai_logs/LuongDucDuy_ai_log.xlsx
@@ -19,225 +19,123 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="321">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
   <si>
+    <t>DETAILED AI AUDIT LOG</t>
+  </si>
+  <si>
+    <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
+  </si>
+  <si>
+    <t>SELF-ASSESSMENT CHECKLIST (Trước khi nộp)</t>
+  </si>
+  <si>
+    <t>Kiểm tra kỹ trước khi nộp. MỖI ENTRY phải pass ≥4/5 tiêu chí dưới đây.</t>
+  </si>
+  <si>
+    <t>INSTRUCTIONS: Chỉ ghi CORE PROMPTS (Decision/Problem-Solving/Verification). Mỗi entry phải trả lời đầy đủ 4 câu hỏi trong Human Delta.</t>
+  </si>
+  <si>
     <t>STUDENT INFORMATION</t>
   </si>
   <si>
+    <t>A. KIỂM TRA CHẤT LƯỢNG MỖI ENTRY (Pass ≥4/5)</t>
+  </si>
+  <si>
+    <t>Entry #</t>
+  </si>
+  <si>
     <t>Student Name:</t>
   </si>
   <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Prompt Type</t>
+  </si>
+  <si>
+    <t>Stage/Component</t>
+  </si>
+  <si>
+    <t>Problem/Context</t>
+  </si>
+  <si>
+    <t>Tiêu chí</t>
+  </si>
+  <si>
+    <t>Prompt to AI</t>
+  </si>
+  <si>
+    <t>AI Response (Summary)</t>
+  </si>
+  <si>
+    <t>Human Delta &amp; Reflection</t>
+  </si>
+  <si>
+    <t>Pass?</t>
+  </si>
+  <si>
+    <t>Evidence</t>
+  </si>
+  <si>
+    <t>MỖI PROJECT PHẢI PHÁT HIỆN ÍT NHẤT: Lab (≥1), Assignment (≥2), Project (≥3) cases hallucination</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
     <t>[Lương Đức Duy]</t>
   </si>
   <si>
-    <t>SELF-ASSESSMENT CHECKLIST (Trước khi nộp)</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Entry # (from Sheet 2)</t>
+  </si>
+  <si>
+    <t>DECISION</t>
+  </si>
+  <si>
+    <t>Decomposition</t>
+  </si>
+  <si>
+    <t>Hallucination Type</t>
   </si>
   <si>
     <t>Student ID:</t>
   </si>
   <si>
-    <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
+    <t>Prompt này ảnh hưởng đến quyết định quan trọng trong project?</t>
+  </si>
+  <si>
+    <t>Cần chia nhỏ requirement</t>
+  </si>
+  <si>
+    <t>AI's Claim</t>
   </si>
   <si>
     <t>[QE200114]</t>
   </si>
   <si>
-    <t>Kiểm tra kỹ trước khi nộp. MỖI ENTRY phải pass ≥4/5 tiêu chí dưới đây.</t>
-  </si>
-  <si>
-    <t>DETAILED AI AUDIT LOG</t>
-  </si>
-  <si>
-    <t>Course:</t>
-  </si>
-  <si>
-    <t>[ LAB211]</t>
-  </si>
-  <si>
-    <t>A. KIỂM TRA CHẤT LƯỢNG MỖI ENTRY (Pass ≥4/5)</t>
-  </si>
-  <si>
-    <t>Assignment:</t>
-  </si>
-  <si>
-    <t>[Football Club]</t>
-  </si>
-  <si>
-    <t>INSTRUCTIONS: Chỉ ghi CORE PROMPTS (Decision/Problem-Solving/Verification). Mỗi entry phải trả lời đầy đủ 4 câu hỏi trong Human Delta.</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>AI USAGE SUMMARY</t>
-  </si>
-  <si>
-    <t>MỖI PROJECT PHẢI PHÁT HIỆN ÍT NHẤT: Lab (≥1), Assignment (≥2), Project (≥3) cases hallucination</t>
-  </si>
-  <si>
-    <t>Total Prompts Used (all AI tools):</t>
-  </si>
-  <si>
-    <t>Core Prompts Logged:</t>
-  </si>
-  <si>
-    <t>Entry #</t>
-  </si>
-  <si>
-    <t>Tiêu chí</t>
-  </si>
-  <si>
-    <t>Prompt Type</t>
-  </si>
-  <si>
-    <t>Entry # (from Sheet 2)</t>
-  </si>
-  <si>
-    <t>Pass?</t>
-  </si>
-  <si>
-    <t>Stage/Component</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>Hallucination Type</t>
-  </si>
-  <si>
-    <t>Problem/Context</t>
-  </si>
-  <si>
-    <t>Selection Ratio:</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>AI's Claim</t>
-  </si>
-  <si>
-    <t>Prompt to AI</t>
+    <t>Break down student management into modules</t>
   </si>
   <si>
     <t>Reality Check</t>
   </si>
   <si>
-    <t>AI Response (Summary)</t>
-  </si>
-  <si>
-    <t>Prompt này ảnh hưởng đến quyết định quan trọng trong project?</t>
+    <t>AI suggested 10 modules: User, Student, Course, Grade, Attendance, Report, Export, Import, Settings, Dashboard</t>
   </si>
   <si>
     <t>How Detected</t>
   </si>
   <si>
-    <t>Human Delta &amp; Reflection</t>
-  </si>
-  <si>
-    <t>Corrective Action</t>
-  </si>
-  <si>
-    <t>☐</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>Evidence</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Nếu không có prompt này, project có thay đổi về architecture/design?</t>
-  </si>
-  <si>
-    <t>001</t>
-  </si>
-  <si>
-    <t>Fabrication</t>
-  </si>
-  <si>
-    <t>Paper 'Smith et al. 2023' exists</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Paper NOT FOUND on Google Scholar</t>
-  </si>
-  <si>
-    <t>Should be 10-20%</t>
-  </si>
-  <si>
-    <t>Tôi có thể giải thích lý do chọn/không chọn gợi ý của AI?</t>
-  </si>
-  <si>
-    <t>Searched Google Scholar, ResearchGate</t>
-  </si>
-  <si>
-    <t>Hallucination Detected:</t>
-  </si>
-  <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>Used real paper 'Jones et al. 2022'</t>
-  </si>
-  <si>
-    <t>Decomposition</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>AI TOOLS USED</t>
-  </si>
-  <si>
-    <t>Có minh chứng cụ thể (code, metrics, comparison)?</t>
-  </si>
-  <si>
-    <t>Cần chia nhỏ requirement</t>
-  </si>
-  <si>
-    <t>Đề xuất thiết kế chưa phù hợp</t>
-  </si>
-  <si>
-    <t>AI Tool</t>
-  </si>
-  <si>
-    <t>Break down student management into modules</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>AI đề xuất thêm actor "Simulator" vào Use Case Diagram</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Simulator không phải actor nghiệp vụ thực tế và không cần xuất hiện trong Use Case Diagram theo UML</t>
-  </si>
-  <si>
-    <t>Đối chiếu với định nghĩa actor trong UML và tài liệu môn học</t>
-  </si>
-  <si>
-    <t>Frequency</t>
-  </si>
-  <si>
-    <t>AI suggested 10 modules: User, Student, Course, Grade, Attendance, Report, Export, Import, Settings, Dashboard</t>
-  </si>
-  <si>
-    <t>Prompt này phản ánh tư duy phản biện, không chỉ copy AI?</t>
-  </si>
-  <si>
-    <t>Loại bỏ Simulator và chỉ giữ các actor Guest, Fan, Staff, Admin</t>
+    <t>☑</t>
   </si>
   <si>
     <t>Critical Thinking: 10 modules quá nhiều cho project 300 LOC.
@@ -246,169 +144,76 @@
 Decision: Chọn 5 modules vì đủ để implement requirements mà không phức tạp.</t>
   </si>
   <si>
-    <t>Hiểu sai yêu cầu hệ thống</t>
-  </si>
-  <si>
-    <t>B. KIỂM TRA TỔNG THỂ LOG</t>
-  </si>
-  <si>
-    <t>AI đề xuất Staff quản lý sân vận động và khu vực ghế</t>
-  </si>
-  <si>
-    <t>Quản lý sân vận động và khu vực ghế thuộc quyền Admin theo yêu cầu dự án</t>
-  </si>
-  <si>
-    <t>Main Value</t>
-  </si>
-  <si>
-    <t>Đối chiếu với đặc tả hệ thống và phân quyền người dùng</t>
-  </si>
-  <si>
-    <t>Chuyển quyền quản lý sân vận động cho Admin và giới hạn Staff ở các chức năng liên quan đến vé</t>
-  </si>
-  <si>
-    <t>ChatGPT</t>
-  </si>
-  <si>
-    <t>Current Value</t>
-  </si>
-  <si>
-    <t>Thiết kế chưa tối ưu</t>
-  </si>
-  <si>
-    <t>Code generation, debugging</t>
-  </si>
-  <si>
-    <t>AI đề xuất tạo nhiều hàm findByEmail(), findByPhone(), findByName() riêng biệt</t>
+    <t>Course:</t>
+  </si>
+  <si>
+    <t>Corrective Action</t>
   </si>
   <si>
     <t>Screenshot comparison 10 vs 5</t>
   </si>
   <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Nhiều hàm gây lặp code và khó mở rộng</t>
-  </si>
-  <si>
-    <t>Số lượng entries nằm trong range (min-max)?</t>
-  </si>
-  <si>
-    <t>So sánh với nguyên lý tái sử dụng code và Functional Interface</t>
-  </si>
-  <si>
-    <t>Rapid prototyping</t>
-  </si>
-  <si>
-    <t>Sử dụng findByCondition(Predicate&lt;Fan&gt;) để hỗ trợ nhiều điều kiện tìm kiếm</t>
-  </si>
-  <si>
-    <t>Claude</t>
-  </si>
-  <si>
-    <t>Requirement analysis, design review</t>
+    <t>[ LAB211]</t>
+  </si>
+  <si>
+    <t>Tất cả 20 entries đều liên quan đến các quyết định kiến trúc, tối ưu thuật toán, cấu hình Maven, và kiểm thử đồng thời (concurrency).</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>Assignment:</t>
   </si>
   <si>
     <t>002</t>
   </si>
   <si>
-    <t>Mỗi DTC component có ít nhất 1 core prompt?</t>
-  </si>
-  <si>
-    <t>Medium</t>
+    <t>[Football Club]</t>
+  </si>
+  <si>
+    <t>Fabrication</t>
   </si>
   <si>
     <t>PROBLEM-SOLVING</t>
   </si>
   <si>
-    <t>Đã phát hiện ≥ số lượng hallucination yêu cầu?</t>
-  </si>
-  <si>
-    <t>Kiểm thử chưa đầy đủ</t>
-  </si>
-  <si>
-    <t>Deep reflection</t>
-  </si>
-  <si>
-    <t>AI chỉ kiểm tra số lượng phần tử trả về</t>
-  </si>
-  <si>
-    <t>Có thể đúng size nhưng sai dữ liệu</t>
-  </si>
-  <si>
-    <t>GitHub Copilot</t>
-  </si>
-  <si>
-    <t>Phân tích trường hợp kết quả trả về sai thứ tự hoặc sai đối tượng</t>
-  </si>
-  <si>
-    <t>Mỗi entry đều có Human Delta đầy đủ (4 câu hỏi)?</t>
-  </si>
-  <si>
-    <t>Bổ sung kiểm tra ID của từng phần tử bằng assertEquals</t>
-  </si>
-  <si>
-    <t>Auto-completion</t>
-  </si>
-  <si>
-    <t>Speed up coding</t>
+    <t>2</t>
+  </si>
+  <si>
+    <t>AI USAGE SUMMARY</t>
+  </si>
+  <si>
+    <t>Paper 'Smith et al. 2023' exists</t>
   </si>
   <si>
     <t>Algorithms</t>
   </si>
   <si>
-    <t>[Add more...]</t>
-  </si>
-  <si>
-    <t>Có evidence cho ≥70% entries?</t>
+    <t>Nếu không có prompt này, project có thay đổi về architecture/design?</t>
+  </si>
+  <si>
+    <t>Paper NOT FOUND on Google Scholar</t>
   </si>
   <si>
     <t>Search by name quá chậm với 10K records</t>
   </si>
   <si>
-    <t>CORE PROMPTS DISTRIBUTION BY DTC COMPONENT</t>
-  </si>
-  <si>
-    <t>⚠️ LƯU Ý QUAN TRỌNG:</t>
+    <t>Total Prompts Used (all AI tools):</t>
+  </si>
+  <si>
+    <t>Searched Google Scholar, ResearchGate</t>
   </si>
   <si>
     <t>How to optimize search for player name in 10,000 records?</t>
   </si>
   <si>
-    <t>DTC Component</t>
-  </si>
-  <si>
-    <t>Nếu entry KHÔNG pass ≥4/5 tiêu chí → LOẠI BỎ, không ghi vào Log</t>
-  </si>
-  <si>
-    <t>Number of Prompts</t>
-  </si>
-  <si>
-    <t>Nếu FAIL ≥2 tiêu chí tổng thể → AI Reflection = 0 điểm (mất 30%)</t>
-  </si>
-  <si>
-    <t>Không có lỗi nghiêm trọng</t>
+    <t>Used real paper 'Jones et al. 2022'</t>
   </si>
   <si>
     <t>AI suggested Binary Search with O(log n) complexity</t>
   </si>
   <si>
-    <t>Required (Min)</t>
-  </si>
-  <si>
-    <t>C. CHUẨN BỊ CHO ORAL VIVAS (Q&amp;A)</t>
-  </si>
-  <si>
-    <t>AI khẳng định testFindByCondition đúng</t>
-  </si>
-  <si>
-    <t>Giảng viên sẽ hỏi ngẫu nhiên về 3-5 entries. Tự hỏi bản thân:</t>
-  </si>
-  <si>
-    <t>Kiểm tra lại mã nguồn cho thấy logic phù hợp với yêu cầu và kết quả mong đợi</t>
-  </si>
-  <si>
-    <t>Đối chiếu với mã nguồn FanRepository và kết quả test</t>
+    <t>Core Prompts Logged:</t>
   </si>
   <si>
     <t>Critical Thinking: Binary Search cần sort trước → O(n log n). Với partial match không phù hợp.
@@ -417,58 +222,37 @@
 Decision: Chọn HashMap trade-off memory cho speed.</t>
   </si>
   <si>
-    <t>Giữ nguyên đoạn test</t>
+    <t>Giúp định hình lại cấu trúc 5 modules, mô hình MVC, cơ chế Locking (Synchronized/Optimistic) và lược bỏ actor Simulator không phù hợp.</t>
   </si>
   <si>
     <t>Code snippet + timing comparison</t>
   </si>
   <si>
-    <t>Tôi có thể giải thích tại sao chọn approach này?</t>
-  </si>
-  <si>
-    <t>≥ 1</t>
+    <t>Đề xuất thiết kế chưa phù hợp</t>
   </si>
   <si>
     <t>VERIFICATION</t>
   </si>
   <si>
-    <t>Tôi có nhớ AI response?</t>
-  </si>
-  <si>
     <t>Literature Review</t>
   </si>
   <si>
-    <t>Cấu hình Maven chưa phù hợp</t>
-  </si>
-  <si>
-    <t>AI đề xuất loại trừ thư mục test bằng &lt;excludes&gt;</t>
-  </si>
-  <si>
-    <t>Tôi có evidence?</t>
+    <t>Selection Ratio:</t>
   </si>
   <si>
     <t>Cần verify paper AI cite</t>
   </si>
   <si>
-    <t>Pattern Recognition</t>
-  </si>
-  <si>
-    <t>Việc loại trừ test khiến Maven không compile và không chạy được JUnit</t>
-  </si>
-  <si>
     <t>Is the paper 'Smith et al. 2023 on IoT anomaly detection' a real publication?</t>
   </si>
   <si>
-    <t>Chạy mvn test và kiểm tra log</t>
-  </si>
-  <si>
-    <t>Xóa phần &lt;excludes&gt; để Maven xử lý cả source và test</t>
+    <t>3</t>
   </si>
   <si>
     <t>AI confirmed it exists and provided summary</t>
   </si>
   <si>
-    <t>Abstraction</t>
+    <t>Tôi có thể giải thích lý do chọn/không chọn gợi ý của AI?</t>
   </si>
   <si>
     <t>Critical Thinking: HALLUCINATION DETECTED! Search Google Scholar → paper NOT FOUND.
@@ -480,40 +264,43 @@
     <t>Google Scholar screenshot</t>
   </si>
   <si>
-    <t>Đề xuất cấu hình chưa đầy đủ</t>
-  </si>
-  <si>
-    <t>AI cho rằng chỉ cần thêm dependency JUnit là đủ</t>
-  </si>
-  <si>
-    <t>Một số môi trường vẫn cần cấu hình Surefire với &lt;useModulePath&gt;false&gt;</t>
+    <t>AI đề xuất thêm actor "Simulator" vào Use Case Diagram</t>
+  </si>
+  <si>
+    <t>Simulator không phải actor nghiệp vụ thực tế và không cần xuất hiện trong Use Case Diagram theo UML</t>
+  </si>
+  <si>
+    <t>Đã ghi rõ lý do phân tích trong Human Delta cho từng entry từ 001 đến 20.</t>
+  </si>
+  <si>
+    <t>Đối chiếu với định nghĩa actor trong UML và tài liệu môn học</t>
+  </si>
+  <si>
+    <t>Loại bỏ Simulator và chỉ giữ các actor Guest, Fan, Staff, Admin</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>Use Case Design</t>
   </si>
   <si>
-    <t>Đối chiếu tài liệu Maven Surefire và kết quả thực tế</t>
-  </si>
-  <si>
     <t>Cần xác định liệu actor Staff có nên được thêm vào hệ thống và quyền hạn của Staff trong hệ thống đặt vé bóng đá.</t>
   </si>
   <si>
-    <t>Bổ sung cấu hình useModulePath=false để đảm bảo khả năng chạy test ổn định</t>
-  </si>
-  <si>
     <t>Staff có nên có các chức năng giống Fan không? Staff có nên quản lý sân vận động và ghế ngồi không?</t>
   </si>
   <si>
-    <t>Tạo SimulatorController sử dụng CountDownLatch và ExecutorService, kết nối với BookingController để xử lý các yêu cầu booking song song.</t>
+    <t>Có minh chứng cụ thể (code, metrics, comparison)?</t>
+  </si>
+  <si>
+    <t>Hiểu sai yêu cầu hệ thống</t>
   </si>
   <si>
     <t>AI đề xuất tách Staff khỏi Fan. Staff nên thực hiện xác thực vé, hỗ trợ đặt vé và hỗ trợ khách hàng. Việc quản lý sân vận động, khu vực, ghế ngồi và trận đấu nên thuộc quyền Admin.</t>
   </si>
   <si>
-    <t>Kiểm tra các class hiện có, cấu trúc MVC, constructor của BookingController, quan hệ với StadiumController và cách booking thực tế được xử lý.</t>
-  </si>
-  <si>
-    <t>Đề xuất phù hợp với kiến trúc project. SimulatorController có thể đặt trong controller và sử dụng controller hiện có.</t>
+    <t>AI đề xuất Staff quản lý sân vận động và khu vực ghế</t>
   </si>
   <si>
     <t>Critical Thinking: Việc cấp toàn bộ quyền của Admin cho Staff sẽ làm mất tính phân quyền của hệ thống.
@@ -522,214 +309,298 @@
 Decision: Giữ Staff là một actor riêng với quyền hạn giới hạn; các chức năng quản lý sân vận động, khu vực và ghế thuộc về Admin.</t>
   </si>
   <si>
-    <t>Không phát hiện hallucination nghiêm trọng. Tuy nhiên AI có thể giả định tên method hoặc constructor dựa trên mô tả.</t>
-  </si>
-  <si>
-    <t>Đối chiếu source code thực tế và chạy Maven compile. Sau khi điều chỉnh, code compile thành công.</t>
+    <t>Quản lý sân vận động và khu vực ghế thuộc quyền Admin theo yêu cầu dự án</t>
   </si>
   <si>
     <t>Use Case Diagram đã cập nhật với các actor Fan, Staff và Admin.</t>
   </si>
   <si>
-    <t>Tạo SimulatorView để hiển thị danh sách BookingResult dưới dạng ASCII table.</t>
-  </si>
-  <si>
-    <t>Kiểm tra BookingResult, các field thực tế, dữ liệu trả về từ SimulatorController và khả năng truyền dữ liệu sang View.</t>
-  </si>
-  <si>
-    <t>Thiết kế phù hợp với dữ liệu kết quả simulator.</t>
-  </si>
-  <si>
-    <t>Không phát hiện hallucination đáng kể. Tuy nhiên tên field hoặc getter cần được đối chiếu với source code thực tế.</t>
-  </si>
-  <si>
-    <t>Kiểm tra class BookingResult và đảm bảo SimulatorView sử dụng đúng field hoặc getter thực tế.</t>
-  </si>
-  <si>
-    <t>Chạy simulator bằng cách khởi tạo BookingController, SimulatorController, SimulatorView và gọi runSimulation() với dữ liệu demo.</t>
-  </si>
-  <si>
-    <t>Kiểm tra constructor, method runSimulation(), method display(), kiểu dữ liệu BookingResult và khả năng compile.</t>
-  </si>
-  <si>
-    <t>Code mẫu thể hiện đúng ý tưởng nhưng có thể chứa giả định về API thực tế của project. Sau đó simulator được tích hợp vào MainView.</t>
-  </si>
-  <si>
-    <t>Có khả năng hallucination ở mức giả định API. AI có thể không biết chính xác constructor hoặc method của project.</t>
-  </si>
-  <si>
-    <t>Không sử dụng code mẫu một cách mù quáng. Kiểm tra source code và Maven compile trước khi tích hợp.</t>
-  </si>
-  <si>
-    <t>AI thông báo Maven compile finished và cả hai class compile cleanly.</t>
-  </si>
-  <si>
-    <t>Kiểm tra trực tiếp kết quả Maven build sau khi thêm SimulatorController, SimulatorView và thay đổi MainView.</t>
-  </si>
-  <si>
-    <t>Maven compile hoàn thành thành công.</t>
+    <t>Đối chiếu với đặc tả hệ thống và phân quyền người dùng</t>
+  </si>
+  <si>
+    <t>Đã ghi kèm bằng chứng screenshot, đoạn code JUnit test, Maven log, và Simulator output.</t>
+  </si>
+  <si>
+    <t>Chuyển quyền quản lý sân vận động cho Admin và giới hạn Staff ở các chức năng liên quan đến vé</t>
   </si>
   <si>
     <t>Thiết kế Use Case</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>Xác định liệu Simulator có nên xuất hiện như một actor trong Use Case Diagram hay không</t>
   </si>
   <si>
-    <t>Không phát hiện hallucination về compilation nếu kết quả Maven được xác nhận trực tiếp. Tuy nhiên compile thành công không chứng minh concurrency logic hoàn toàn đúng.</t>
-  </si>
-  <si>
     <t>Có thể bỏ Simulator khỏi Use Case Diagram được không?</t>
   </si>
   <si>
-    <t>Phân biệt compile correctness, functional correctness và concurrency correctness. Tiếp tục kiểm thử runtime và race condition.</t>
+    <t>Should be 10-20%</t>
   </si>
   <si>
     <t>AI giải thích rằng Simulator là công cụ kiểm thử, không phải actor nghiệp vụ thực tế và thường không xuất hiện trong Use Case Diagram.</t>
   </si>
   <si>
+    <t>Thiết kế chưa tối ưu</t>
+  </si>
+  <si>
+    <t>Prompt này phản ánh tư duy phản biện, không chỉ copy AI?</t>
+  </si>
+  <si>
     <t>Critical Thinking: Use Case Diagram mô tả sự tương tác giữa người dùng và hệ thống. Simulator không phải người dùng thực tế. Contextualization: Chức năng chống double booking được xử lý thông qua version của Seat và BookingTransaction. Creative Synthesis: Chuyển việc mô phỏng đặt vé đồng thời sang giai đoạn kiểm thử thay vì biểu diễn như một actor. Decision: Loại bỏ Simulator khỏi Use Case Diagram và chỉ giữ Guest, Fan, Staff, Admin.</t>
   </si>
   <si>
-    <t>AI thông báo đã thêm Run Booking Simulator, handler trong main loop, runSimulatorFlow() và option 9.</t>
+    <t>AI đề xuất tạo nhiều hàm findByEmail(), findByPhone(), findByName() riêng biệt</t>
   </si>
   <si>
     <t>Use Case Diagram đã được cập nhật và loại bỏ Simulator.</t>
   </si>
   <si>
-    <t>Kiểm tra MainView, menu option 9, runSimulatorFlow(), quá trình chạy simulator và kết quả hiển thị.</t>
-  </si>
-  <si>
-    <t>Simulator được tích hợp vào MainView và có thể khởi chạy từ option 9.</t>
-  </si>
-  <si>
-    <t>Không phát hiện hallucination nghiêm trọng nếu các thay đổi tồn tại thực tế trong source code.</t>
-  </si>
-  <si>
-    <t>Xác minh trực tiếp source code, chạy Maven compile và kiểm tra runtime để xác nhận simulator hoạt động đúng.</t>
+    <t>Hallucination Detected:</t>
+  </si>
+  <si>
+    <t>Nhiều hàm gây lặp code và khó mở rộng</t>
+  </si>
+  <si>
+    <t>So sánh với nguyên lý tái sử dụng code và Functional Interface</t>
   </si>
   <si>
     <t>FanRepository - Search</t>
   </si>
   <si>
+    <t>Thể hiện qua việc phát hiện tài liệu ảo, loại bỏ thiết kế dư thừa của AI và tối ưu lại logic kiểm thử.</t>
+  </si>
+  <si>
     <t>Cần tìm kiếm Fan theo nhiều tiêu chí mà không muốn viết nhiều hàm riêng như findByEmail(), findByPhone(), findByBirthYear()</t>
   </si>
   <si>
+    <t>Sử dụng findByCondition(Predicate&lt;Fan&gt;) để hỗ trợ nhiều điều kiện tìm kiếm</t>
+  </si>
+  <si>
     <t>Làm thế nào để thiết kế chức năng tìm kiếm linh hoạt cho FanRepository?</t>
   </si>
   <si>
+    <t>AI TOOLS USED</t>
+  </si>
+  <si>
     <t>AI đề xuất sử dụng Predicate&lt;Fan&gt; và một hàm findByCondition() để truyền điều kiện tìm kiếm bằng lambda expression.</t>
   </si>
   <si>
+    <t>B. KIỂM TRA TỔNG THỂ LOG</t>
+  </si>
+  <si>
     <t>Critical Thinking: Viết nhiều hàm tìm kiếm sẽ gây lặp code và khó bảo trì. Contextualization: Dự án cần tìm theo email, số điện thoại, tên và năm sinh. Creative Synthesis: Sử dụng Predicate&lt;Fan&gt; để tái sử dụng một hàm cho mọi điều kiện. Decision: Chọn findByCondition() để tăng tính mở rộng và giảm trùng lặp code.</t>
   </si>
   <si>
+    <t>AI Tool</t>
+  </si>
+  <si>
     <t>Code FanRepository và JUnit test</t>
   </si>
   <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
     <t>Unit Test</t>
   </si>
   <si>
     <t>Cần kiểm tra chức năng tìm kiếm theo năm sinh hoạt động chính xác</t>
   </si>
   <si>
+    <t>Main Value</t>
+  </si>
+  <si>
     <t>Viết test cho findByCondition với birthYear</t>
   </si>
   <si>
     <t>AI đề xuất sử dụng f -&gt; f.getBirthYear() == 2000 và kiểm tra số lượng phần tử trả về</t>
   </si>
   <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
     <t>Critical Thinking: Chỉ kiểm tra size chưa đủ để đảm bảo dữ liệu đúng. Contextualization: Cần xác minh ID của từng phần tử trong kết quả. Creative Synthesis: Bổ sung assertEquals cho ID F001 và F003. Decision: Kiểm tra cả size và dữ liệu thực tế của từng đối tượng.</t>
   </si>
   <si>
+    <t>Code generation, debugging</t>
+  </si>
+  <si>
     <t>JUnit testFindByBirthYear()</t>
   </si>
   <si>
+    <t>Current Value</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Rapid prototyping</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>Số lượng entries nằm trong range (min-max)?</t>
+  </si>
+  <si>
+    <t>Requirement analysis, design review</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Kiểm thử chưa đầy đủ</t>
+  </si>
+  <si>
+    <t>Deep reflection</t>
+  </si>
+  <si>
+    <t>20 entries</t>
+  </si>
+  <si>
+    <t>AI chỉ kiểm tra số lượng phần tử trả về</t>
+  </si>
+  <si>
+    <t>Có thể đúng size nhưng sai dữ liệu</t>
+  </si>
+  <si>
+    <t>GitHub Copilot</t>
+  </si>
+  <si>
+    <t>Phân tích trường hợp kết quả trả về sai thứ tự hoặc sai đối tượng</t>
+  </si>
+  <si>
+    <t>Auto-completion</t>
+  </si>
+  <si>
     <t>Code Generation</t>
   </si>
   <si>
-    <t>HALLUCINATION TYPES REFERENCE:</t>
+    <t>Bổ sung kiểm tra ID của từng phần tử bằng assertEquals</t>
+  </si>
+  <si>
+    <t>Mỗi DTC component có ít nhất 1 core prompt?</t>
+  </si>
+  <si>
+    <t>Speed up coding</t>
+  </si>
+  <si>
+    <t>[Add more...]</t>
   </si>
   <si>
     <t>FanRepositoryTest</t>
   </si>
   <si>
-    <t>Type</t>
+    <t>Đã phủ đủ Decomposition, Algorithms, Architecture/Design, Verification &amp; Code Gen</t>
   </si>
   <si>
     <t>Cần tạo test kiểm tra chức năng tìm kiếm theo điều kiện trong FanRepository</t>
   </si>
   <si>
-    <t>Definition</t>
-  </si>
-  <si>
     <t>Viết JUnit test cho hàm findByCondition để lọc các Fan có email chứa "gmail"</t>
   </si>
   <si>
-    <t>Example</t>
+    <t>Đã phát hiện ≥ số lượng hallucination yêu cầu?</t>
   </si>
   <si>
     <t>AI tạo test thêm 3 Fan, lọc email chứa gmail và kiểm tra số lượng kết quả cùng ID của từng phần tử</t>
   </si>
   <si>
-    <t>AI tạo ra thông tin không tồn tại</t>
+    <t>CORE PROMPTS DISTRIBUTION BY DTC COMPONENT</t>
+  </si>
+  <si>
+    <t>DTC Component</t>
+  </si>
+  <si>
+    <t>8 cases (Yêu cầu Assignment: ≥2 cases)</t>
+  </si>
+  <si>
+    <t>Number of Prompts</t>
   </si>
   <si>
     <t>Kiểm tra lại logic, xác nhận kết quả mong muốn là F001 và F003, chỉnh sửa mô tả để dễ hiểu hơn</t>
   </si>
   <si>
-    <t>Fake papers, fake APIs, fake data</t>
-  </si>
-  <si>
-    <t>Oversimplification</t>
+    <t>Required (Min)</t>
   </si>
   <si>
     <t>Ảnh chụp mã nguồn testFindByCondition</t>
   </si>
   <si>
-    <t>AI bỏ qua edge cases, exceptions</t>
-  </si>
-  <si>
-    <t>Code không handle array rỗng</t>
-  </si>
-  <si>
-    <t>Logic Error</t>
-  </si>
-  <si>
-    <t>AI đưa kết luận sai về 'best practice'</t>
-  </si>
-  <si>
-    <t>'XGBoost always best' → Sai</t>
-  </si>
-  <si>
-    <t>Outdated Info</t>
-  </si>
-  <si>
-    <t>AI dùng thông tin cũ, không còn đúng</t>
-  </si>
-  <si>
-    <t>Old API syntax, deprecated methods</t>
-  </si>
-  <si>
-    <t>Context Misunderstanding</t>
-  </si>
-  <si>
-    <t>AI không hiểu đúng bối cảnh</t>
-  </si>
-  <si>
-    <t>Không biết business constraints</t>
+    <t>Không có lỗi nghiêm trọng</t>
+  </si>
+  <si>
+    <t>Mỗi entry đều có Human Delta đầy đủ (4 câu hỏi)?</t>
+  </si>
+  <si>
+    <t>AI khẳng định testFindByCondition đúng</t>
+  </si>
+  <si>
+    <t>Kiểm tra lại mã nguồn cho thấy logic phù hợp với yêu cầu và kết quả mong đợi</t>
+  </si>
+  <si>
+    <t>≥ 1</t>
+  </si>
+  <si>
+    <t>100% entries đáp ứng đủ 4 câu hỏi (Critical Thinking, Contextualization, Creative Synthesis, Decision)</t>
+  </si>
+  <si>
+    <t>Đối chiếu với mã nguồn FanRepository và kết quả test</t>
+  </si>
+  <si>
+    <t>Giữ nguyên đoạn test</t>
+  </si>
+  <si>
+    <t>Pattern Recognition</t>
+  </si>
+  <si>
+    <t>Có evidence cho ≥70% entries?</t>
+  </si>
+  <si>
+    <t>Abstraction</t>
+  </si>
+  <si>
+    <t>100% (20/20 entries đều có Evidence)</t>
+  </si>
+  <si>
+    <t>⚠️ LƯU Ý QUAN TRỌNG:</t>
+  </si>
+  <si>
+    <t>Nếu entry KHÔNG pass ≥4/5 tiêu chí → LOẠI BỎ, không ghi vào Log</t>
+  </si>
+  <si>
+    <t>Nếu FAIL ≥2 tiêu chí tổng thể → AI Reflection = 0 điểm (mất 30%)</t>
+  </si>
+  <si>
+    <t>C. CHUẨN BỊ CHO ORAL VIVAS (Q&amp;A)</t>
   </si>
   <si>
     <t>Maven Configuration</t>
   </si>
   <si>
+    <t>Giảng viên sẽ hỏi ngẫu nhiên về 3-5 entries. Tự hỏi bản thân:</t>
+  </si>
+  <si>
     <t>Maven không chạy được JUnit test do cấu hình loại trừ thư mục test.</t>
   </si>
   <si>
+    <t>Cấu hình Maven chưa phù hợp</t>
+  </si>
+  <si>
     <t>Kiểm tra cấu hình Maven và tìm nguyên nhân khiến JUnit không chạy.</t>
   </si>
   <si>
+    <t>AI đề xuất loại trừ thư mục test bằng &lt;excludes&gt;</t>
+  </si>
+  <si>
     <t>AI phát hiện phần &lt;excludes&gt; trong maven-compiler-plugin đang loại bỏ các file test khỏi quá trình compile.</t>
+  </si>
+  <si>
+    <t>Việc loại trừ test khiến Maven không compile và không chạy được JUnit</t>
   </si>
   <si>
     <t>Critical Thinking: Nếu loại trừ thư mục test thì Maven sẽ không compile và chạy được JUnit.
@@ -738,19 +609,100 @@
 Decision: Giữ cấu hình mặc định của Maven để đảm bảo các test được thực thi bình thường.</t>
   </si>
   <si>
+    <t>Chạy mvn test và kiểm tra log</t>
+  </si>
+  <si>
+    <t>Tôi có thể giải thích tại sao chọn approach này?</t>
+  </si>
+  <si>
     <t>So sánh kết quả mvn test trước và sau khi xóa &lt;excludes&gt;.</t>
   </si>
   <si>
+    <t>Xóa phần &lt;excludes&gt; để Maven xử lý cả source và test</t>
+  </si>
+  <si>
+    <t>Tôi có nhớ AI response?</t>
+  </si>
+  <si>
+    <t>Đề xuất cấu hình chưa đầy đủ</t>
+  </si>
+  <si>
+    <t>Tôi có evidence?</t>
+  </si>
+  <si>
+    <t>AI cho rằng chỉ cần thêm dependency JUnit là đủ</t>
+  </si>
+  <si>
+    <t>Một số môi trường vẫn cần cấu hình Surefire với &lt;useModulePath&gt;false&gt;</t>
+  </si>
+  <si>
+    <t>Co gọn từ 10 modules xuống 5 modules vì project scope nhỏ (300 LOC), tránh phức tạp hóa hệ thống.</t>
+  </si>
+  <si>
+    <t>có,AI gợi ý 10 modules (User, Course, Grade, Report, v.v.).</t>
+  </si>
+  <si>
+    <t>Đối chiếu tài liệu Maven Surefire và kết quả thực tế</t>
+  </si>
+  <si>
+    <t>Screenshot so sánh 10 vs 5 modules.</t>
+  </si>
+  <si>
+    <t>Bổ sung cấu hình useModulePath=false để đảm bảo khả năng chạy test ổn định</t>
+  </si>
+  <si>
+    <t>Dùng HashMap thay vì Binary Search vì yêu cầu tìm kiếm partial match và tối ưu tốc độ truy cập.</t>
+  </si>
+  <si>
+    <t>có, AI đề xuất Binary Search O(log n)</t>
+  </si>
+  <si>
+    <t>Tạo SimulatorController sử dụng CountDownLatch và ExecutorService, kết nối với BookingController để xử lý các yêu cầu booking song song.</t>
+  </si>
+  <si>
+    <t>Kiểm tra các class hiện có, cấu trúc MVC, constructor của BookingController, quan hệ với StadiumController và cách booking thực tế được xử lý.</t>
+  </si>
+  <si>
+    <t>Đề xuất phù hợp với kiến trúc project. SimulatorController có thể đặt trong controller và sử dụng controller hiện có.</t>
+  </si>
+  <si>
+    <t>Code snippet + timing comparison (2ms).</t>
+  </si>
+  <si>
+    <t>Không phát hiện hallucination nghiêm trọng. Tuy nhiên AI có thể giả định tên method hoặc constructor dựa trên mô tả.</t>
+  </si>
+  <si>
     <t>Surefire Plugin</t>
   </si>
   <si>
     <t>Kiểm tra khả năng tương thích giữa JUnit 5 và Maven Surefire Plugin.</t>
   </si>
   <si>
+    <t>Tách Staff khỏi Fan và không cấp quyền Admin cho Staff để bảo đảm nguyên tắc phân quyền.</t>
+  </si>
+  <si>
+    <t>Đối chiếu source code thực tế và chạy Maven compile. Sau khi điều chỉnh, code compile thành công.</t>
+  </si>
+  <si>
+    <t>AI đề xuất tách Staff khỏi Fan nhưng cho quản lý sân vận động.</t>
+  </si>
+  <si>
     <t>Xác minh cấu hình JUnit 5 với maven-surefire-plugin 3.2.5.</t>
   </si>
   <si>
+    <t>Use Case Diagram đã cập nhật.</t>
+  </si>
+  <si>
+    <t>Tạo SimulatorView để hiển thị danh sách BookingResult dưới dạng ASCII table.</t>
+  </si>
+  <si>
     <t>AI đề xuất thêm cấu hình &lt;useModulePath&gt;false&lt;/useModulePath&gt; để tránh lỗi nhận diện test trong một số môi trường.</t>
+  </si>
+  <si>
+    <t>Kiểm tra BookingResult, các field thực tế, dữ liệu trả về từ SimulatorController và khả năng truyền dữ liệu sang View.</t>
+  </si>
+  <si>
+    <t>Thiết kế phù hợp với dữ liệu kết quả simulator.</t>
   </si>
   <si>
     <t>Critical Thinking: JUnit 5 đã được hỗ trợ bởi Surefire 3.2.5, nhưng một số IDE hoặc cấu hình module có thể gây lỗi.
@@ -759,12 +711,63 @@
 Decision: Giữ cấu hình này nhằm tránh lỗi khi chạy test trên các môi trường khác nhau.</t>
   </si>
   <si>
+    <t>Không phát hiện hallucination đáng kể. Tuy nhiên tên field hoặc getter cần được đối chiếu với source code thực tế.</t>
+  </si>
+  <si>
+    <t>Kiểm tra class BookingResult và đảm bảo SimulatorView sử dụng đúng field hoặc getter thực tế.</t>
+  </si>
+  <si>
     <t>Kết quả mvn test chạy thành công sau khi cập nhật plugin.</t>
   </si>
   <si>
+    <t>Chạy simulator bằng cách khởi tạo BookingController, SimulatorController, SimulatorView và gọi runSimulation() với dữ liệu demo.</t>
+  </si>
+  <si>
+    <t>Kiểm tra constructor, method runSimulation(), method display(), kiểu dữ liệu BookingResult và khả năng compile.</t>
+  </si>
+  <si>
+    <t>Code mẫu thể hiện đúng ý tưởng nhưng có thể chứa giả định về API thực tế của project. Sau đó simulator được tích hợp vào MainView.</t>
+  </si>
+  <si>
+    <t>Có khả năng hallucination ở mức giả định API. AI có thể không biết chính xác constructor hoặc method của project.</t>
+  </si>
+  <si>
+    <t>Không sử dụng code mẫu một cách mù quáng. Kiểm tra source code và Maven compile trước khi tích hợp.</t>
+  </si>
+  <si>
+    <t>AI thông báo Maven compile finished và cả hai class compile cleanly.</t>
+  </si>
+  <si>
+    <t>Kiểm tra trực tiếp kết quả Maven build sau khi thêm SimulatorController, SimulatorView và thay đổi MainView.</t>
+  </si>
+  <si>
+    <t>Maven compile hoàn thành thành công.</t>
+  </si>
+  <si>
+    <t>Không phát hiện hallucination về compilation nếu kết quả Maven được xác nhận trực tiếp. Tuy nhiên compile thành công không chứng minh concurrency logic hoàn toàn đúng.</t>
+  </si>
+  <si>
+    <t>Phân biệt compile correctness, functional correctness và concurrency correctness. Tiếp tục kiểm thử runtime và race condition.</t>
+  </si>
+  <si>
+    <t>AI thông báo đã thêm Run Booking Simulator, handler trong main loop, runSimulatorFlow() và option 9.</t>
+  </si>
+  <si>
+    <t>Kiểm tra MainView, menu option 9, runSimulatorFlow(), quá trình chạy simulator và kết quả hiển thị.</t>
+  </si>
+  <si>
+    <t>Simulator được tích hợp vào MainView và có thể khởi chạy từ option 9.</t>
+  </si>
+  <si>
     <t>CODE</t>
   </si>
   <si>
+    <t>Không phát hiện hallucination nghiêm trọng nếu các thay đổi tồn tại thực tế trong source code.</t>
+  </si>
+  <si>
+    <t>Xác minh trực tiếp source code, chạy Maven compile và kiểm tra runtime để xác nhận simulator hoạt động đúng.</t>
+  </si>
+  <si>
     <t>AI triển khai SimulatorController để mô phỏng nhiều yêu cầu đặt vé đồng thời. ExecutorService quản lý Thread Pool, CountDownLatch đồng bộ các luồng. Mỗi task đại diện cho một yêu cầu booking và kết quả được lưu trong BookingResult gồm Fan ID, Match ID, Seat ID, trạng thái thành công/thất bại, Transaction ID và Error Message.</t>
   </si>
   <si>
@@ -943,6 +946,60 @@
   </si>
   <si>
     <t>SimulatorView.java; kết quả chạy trên Windows Terminal.</t>
+  </si>
+  <si>
+    <t>HALLUCINATION TYPES REFERENCE:</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Example</t>
+  </si>
+  <si>
+    <t>AI tạo ra thông tin không tồn tại</t>
+  </si>
+  <si>
+    <t>Fake papers, fake APIs, fake data</t>
+  </si>
+  <si>
+    <t>Oversimplification</t>
+  </si>
+  <si>
+    <t>AI bỏ qua edge cases, exceptions</t>
+  </si>
+  <si>
+    <t>Code không handle array rỗng</t>
+  </si>
+  <si>
+    <t>Logic Error</t>
+  </si>
+  <si>
+    <t>AI đưa kết luận sai về 'best practice'</t>
+  </si>
+  <si>
+    <t>'XGBoost always best' → Sai</t>
+  </si>
+  <si>
+    <t>Outdated Info</t>
+  </si>
+  <si>
+    <t>AI dùng thông tin cũ, không còn đúng</t>
+  </si>
+  <si>
+    <t>Old API syntax, deprecated methods</t>
+  </si>
+  <si>
+    <t>Context Misunderstanding</t>
+  </si>
+  <si>
+    <t>AI không hiểu đúng bối cảnh</t>
+  </si>
+  <si>
+    <t>Không biết business constraints</t>
   </si>
 </sst>
 </file>
@@ -952,7 +1009,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -966,6 +1023,12 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <i/>
+      <sz val="10.0"/>
+      <color rgb="FF666666"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <sz val="14.0"/>
       <color rgb="FF2E75B6"/>
@@ -974,23 +1037,7 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10.0"/>
-      <color rgb="FF666666"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1002,7 +1049,7 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1013,8 +1060,27 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1038,11 +1104,6 @@
       <i/>
       <sz val="10.0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1098,86 +1159,98 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1419,211 +1492,211 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
+      <c r="A3" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>3</v>
+      <c r="A4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>7</v>
+      <c r="A5" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>11</v>
+      <c r="A6" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>14</v>
+      <c r="A7" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>17</v>
+      <c r="A9" s="4" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="A10" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="14">
         <v>150.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="12">
+      <c r="A11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="17">
         <v>18.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="16">
+      <c r="A12" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="23">
         <f>C11/C10</f>
         <v>0.12</v>
       </c>
-      <c r="E12" s="17" t="s">
-        <v>50</v>
+      <c r="E12" s="24" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="12">
+      <c r="A13" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C13" s="17">
         <v>2.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>58</v>
+      <c r="A15" s="4" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>78</v>
+      <c r="A16" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>91</v>
+      <c r="A17" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>101</v>
+      <c r="A18" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>109</v>
+      <c r="A19" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
+      <c r="A20" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>114</v>
+      <c r="A22" s="4" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>123</v>
+      <c r="A23" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="B24" s="24">
+      <c r="A24" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="27">
         <v>5.0</v>
       </c>
-      <c r="C24" s="26" t="s">
-        <v>133</v>
+      <c r="C24" s="28" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B25" s="24">
+      <c r="A25" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" s="27">
         <v>4.0</v>
       </c>
-      <c r="C25" s="26" t="s">
-        <v>133</v>
+      <c r="C25" s="28" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="B26" s="24">
+      <c r="A26" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="B26" s="27">
         <v>4.0</v>
       </c>
-      <c r="C26" s="26" t="s">
-        <v>133</v>
+      <c r="C26" s="28" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="B27" s="24">
+      <c r="A27" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="27">
         <v>5.0</v>
       </c>
-      <c r="C27" s="26" t="s">
-        <v>133</v>
+      <c r="C27" s="28" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
@@ -2629,661 +2702,661 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" ht="30.0" customHeight="1">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" ht="39.75" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" ht="39.75" customHeight="1">
-      <c r="A3" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="F3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" ht="99.75" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" s="9" t="s">
+      <c r="C4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" ht="99.75" customHeight="1">
-      <c r="A4" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="15" t="s">
+    <row r="5" ht="99.75" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="D5" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="15" t="s">
+      <c r="F5" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" ht="99.75" customHeight="1">
+      <c r="A6" s="10">
+        <v>3.0</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" ht="79.5" customHeight="1">
+      <c r="A7" s="20">
+        <v>4.0</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="5" ht="99.75" customHeight="1">
-      <c r="A5" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="15" t="s">
+      <c r="F7" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" ht="79.5" customHeight="1">
+      <c r="A8" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" ht="79.5" customHeight="1">
+      <c r="A9" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="6" ht="99.75" customHeight="1">
-      <c r="A6" s="15">
-        <v>3.0</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="G6" s="15" t="s">
+      <c r="E9" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" ht="79.5" customHeight="1">
+      <c r="A10" s="10">
+        <v>7.0</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="21"/>
+      <c r="U10" s="21"/>
+      <c r="V10" s="21"/>
+      <c r="W10" s="21"/>
+      <c r="X10" s="21"/>
+      <c r="Y10" s="21"/>
+      <c r="Z10" s="21"/>
+    </row>
+    <row r="11" ht="79.5" customHeight="1">
+      <c r="A11" s="10">
+        <v>8.0</v>
+      </c>
+      <c r="B11" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="H6" s="15" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" ht="79.5" customHeight="1">
-      <c r="A7" s="27">
-        <v>4.0</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="19" t="s">
+      <c r="C11" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D11" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="H7" s="18" t="s">
+      <c r="E11" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="8" ht="79.5" customHeight="1">
-      <c r="A8" s="19">
-        <v>5.0</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="E8" s="18" t="s">
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+    </row>
+    <row r="12" ht="79.5" customHeight="1">
+      <c r="A12" s="10">
+        <v>9.0</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="D12" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="G8" s="29" t="s">
-        <v>185</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="9" ht="79.5" customHeight="1">
-      <c r="A9" s="19">
-        <v>6.0</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>192</v>
-      </c>
-      <c r="D9" s="18" t="s">
+      <c r="E12" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E9" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="10" ht="79.5" customHeight="1">
-      <c r="A10" s="15">
-        <v>7.0</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>198</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>199</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="I10" s="19"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="19"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
-      <c r="S10" s="19"/>
-      <c r="T10" s="19"/>
-      <c r="U10" s="19"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="19"/>
-      <c r="X10" s="19"/>
-      <c r="Y10" s="19"/>
-      <c r="Z10" s="19"/>
-    </row>
-    <row r="11" ht="79.5" customHeight="1">
-      <c r="A11" s="15">
-        <v>8.0</v>
-      </c>
-      <c r="B11" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11" s="31" t="s">
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+    </row>
+    <row r="13" ht="79.5" customHeight="1">
+      <c r="A13" s="10">
+        <v>10.0</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="G11" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="H11" s="15" t="s">
+      <c r="D13" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="30"/>
-      <c r="T11" s="30"/>
-      <c r="U11" s="30"/>
-      <c r="V11" s="30"/>
-      <c r="W11" s="30"/>
-      <c r="X11" s="30"/>
-      <c r="Y11" s="30"/>
-      <c r="Z11" s="30"/>
-    </row>
-    <row r="12" ht="79.5" customHeight="1">
-      <c r="A12" s="15">
-        <v>9.0</v>
-      </c>
-      <c r="B12" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>230</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="F12" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="30"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
-      <c r="O12" s="30"/>
-      <c r="P12" s="30"/>
-      <c r="Q12" s="30"/>
-      <c r="R12" s="30"/>
-      <c r="S12" s="30"/>
-      <c r="T12" s="30"/>
-      <c r="U12" s="30"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-    </row>
-    <row r="13" ht="79.5" customHeight="1">
-      <c r="A13" s="15">
-        <v>10.0</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>238</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="H13" s="15" t="s">
+      <c r="F13" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
+    </row>
+    <row r="14" ht="79.5" customHeight="1">
+      <c r="A14" s="35">
+        <v>11.0</v>
+      </c>
+      <c r="B14" s="35" t="s">
         <v>240</v>
       </c>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
-      <c r="O13" s="30"/>
-      <c r="P13" s="30"/>
-      <c r="Q13" s="30"/>
-      <c r="R13" s="30"/>
-      <c r="S13" s="30"/>
-      <c r="T13" s="30"/>
-      <c r="U13" s="30"/>
-      <c r="V13" s="30"/>
-      <c r="W13" s="30"/>
-      <c r="X13" s="30"/>
-      <c r="Y13" s="30"/>
-      <c r="Z13" s="30"/>
-    </row>
-    <row r="14" ht="79.5" customHeight="1">
-      <c r="A14" s="28">
-        <v>11.0</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="D14" s="28" t="s">
+      <c r="C14" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="D14" s="35" t="s">
         <v>244</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="E14" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="F14" s="35" t="s">
         <v>246</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="G14" s="35" t="s">
         <v>247</v>
       </c>
+      <c r="H14" s="35" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="15" ht="79.5" customHeight="1">
-      <c r="A15" s="28">
+      <c r="A15" s="35">
         <v>12.0</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>248</v>
-      </c>
-      <c r="D15" s="28" t="s">
+      <c r="B15" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="E15" s="28" t="s">
+      <c r="D15" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="28" t="s">
+      <c r="E15" s="35" t="s">
         <v>251</v>
       </c>
-      <c r="G15" s="28" t="s">
+      <c r="F15" s="35" t="s">
         <v>252</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="G15" s="35" t="s">
         <v>253</v>
       </c>
+      <c r="H15" s="35" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="16" ht="79.5" customHeight="1">
-      <c r="A16" s="28">
+      <c r="A16" s="35">
         <v>13.0</v>
       </c>
-      <c r="B16" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>254</v>
-      </c>
-      <c r="D16" s="28" t="s">
+      <c r="B16" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="D16" s="35" t="s">
         <v>256</v>
       </c>
-      <c r="F16" s="28" t="s">
+      <c r="E16" s="35" t="s">
         <v>257</v>
       </c>
-      <c r="G16" s="28" t="s">
+      <c r="F16" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="H16" s="28" t="s">
+      <c r="G16" s="35" t="s">
         <v>259</v>
       </c>
+      <c r="H16" s="35" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="17" ht="79.5" customHeight="1">
-      <c r="A17" s="32">
+      <c r="A17" s="10">
         <v>14.0</v>
       </c>
-      <c r="B17" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="D17" s="28" t="s">
+      <c r="B17" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="35" t="s">
         <v>261</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="D17" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="E17" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="G17" s="28" t="s">
+      <c r="F17" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H17" s="28" t="s">
+      <c r="G17" s="35" t="s">
         <v>265</v>
       </c>
+      <c r="H17" s="35" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="18" ht="79.5" customHeight="1">
-      <c r="A18" s="28">
+      <c r="A18" s="35">
         <v>15.0</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="D18" s="28" t="s">
+      <c r="B18" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="C18" s="35" t="s">
         <v>267</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="D18" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="E18" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="F18" s="35" t="s">
         <v>270</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="G18" s="35" t="s">
         <v>271</v>
       </c>
+      <c r="H18" s="35" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="19" ht="79.5" customHeight="1">
-      <c r="A19" s="28">
+      <c r="A19" s="35">
         <v>16.0</v>
       </c>
-      <c r="B19" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="28" t="s">
-        <v>272</v>
-      </c>
-      <c r="D19" s="28" t="s">
+      <c r="B19" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="E19" s="28" t="s">
+      <c r="D19" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="F19" s="28" t="s">
+      <c r="E19" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="G19" s="28" t="s">
+      <c r="F19" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="G19" s="35" t="s">
         <v>277</v>
       </c>
+      <c r="H19" s="35" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="20" ht="79.5" customHeight="1">
-      <c r="A20" s="28">
+      <c r="A20" s="35">
         <v>17.0</v>
       </c>
-      <c r="B20" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" s="28" t="s">
-        <v>278</v>
-      </c>
-      <c r="D20" s="28" t="s">
+      <c r="B20" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="D20" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="E20" s="35" t="s">
         <v>281</v>
       </c>
-      <c r="G20" s="28" t="s">
+      <c r="F20" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="H20" s="28" t="s">
+      <c r="G20" s="35" t="s">
         <v>283</v>
       </c>
+      <c r="H20" s="35" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="21" ht="79.5" customHeight="1">
-      <c r="A21" s="28">
+      <c r="A21" s="35">
         <v>18.0</v>
       </c>
-      <c r="B21" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="C21" s="28" t="s">
-        <v>284</v>
-      </c>
-      <c r="D21" s="28" t="s">
+      <c r="B21" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="35" t="s">
         <v>285</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="D21" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="E21" s="35" t="s">
         <v>287</v>
       </c>
-      <c r="G21" s="28" t="s">
+      <c r="F21" s="35" t="s">
         <v>288</v>
       </c>
-      <c r="H21" s="28" t="s">
+      <c r="G21" s="35" t="s">
         <v>289</v>
       </c>
+      <c r="H21" s="35" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="22" ht="79.5" customHeight="1">
-      <c r="A22" s="28">
+      <c r="A22" s="35">
         <v>19.0</v>
       </c>
-      <c r="B22" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>290</v>
-      </c>
-      <c r="D22" s="28" t="s">
+      <c r="B22" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="C22" s="35" t="s">
         <v>291</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="D22" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="E22" s="35" t="s">
         <v>293</v>
       </c>
-      <c r="G22" s="28" t="s">
+      <c r="F22" s="35" t="s">
         <v>294</v>
       </c>
-      <c r="H22" s="28" t="s">
+      <c r="G22" s="35" t="s">
         <v>295</v>
       </c>
+      <c r="H22" s="35" t="s">
+        <v>296</v>
+      </c>
     </row>
     <row r="23" ht="79.5" customHeight="1">
-      <c r="A23" s="28">
+      <c r="A23" s="35">
         <v>20.0</v>
       </c>
-      <c r="B23" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="C23" s="28" t="s">
-        <v>296</v>
-      </c>
-      <c r="D23" s="28" t="s">
+      <c r="B23" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" s="35" t="s">
         <v>297</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="D23" s="35" t="s">
         <v>298</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="E23" s="35" t="s">
         <v>299</v>
       </c>
-      <c r="G23" s="28" t="s">
+      <c r="F23" s="35" t="s">
         <v>300</v>
       </c>
-      <c r="H23" s="28" t="s">
+      <c r="G23" s="35" t="s">
         <v>301</v>
       </c>
+      <c r="H23" s="35" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="24" ht="79.5" customHeight="1">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
     </row>
     <row r="25" ht="79.5" customHeight="1">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
     </row>
     <row r="26" ht="79.5" customHeight="1">
-      <c r="A26" s="15"/>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
     <row r="28" ht="15.75" customHeight="1"/>
@@ -4285,418 +4358,418 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="s">
-        <v>6</v>
+      <c r="A1" s="6" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>18</v>
+      <c r="A2" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3" ht="39.75" customHeight="1">
-      <c r="A3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="A3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>39</v>
+      <c r="F3" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" ht="60.0" customHeight="1">
-      <c r="A4" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="A4" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>55</v>
+      <c r="C4" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15">
+      <c r="A5" s="10">
         <v>4.0</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>72</v>
+      <c r="C5" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="6" ht="60.0" customHeight="1">
-      <c r="A6" s="19">
+      <c r="A6" s="21">
         <v>5.0</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>80</v>
+      <c r="B6" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" ht="60.0" customHeight="1">
-      <c r="A7" s="19">
+      <c r="A7" s="21">
         <v>6.0</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>92</v>
-      </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="T7" s="19"/>
-      <c r="U7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-      <c r="X7" s="19"/>
-      <c r="Y7" s="19"/>
-      <c r="Z7" s="19"/>
+      <c r="B7" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="21"/>
+      <c r="U7" s="21"/>
+      <c r="V7" s="21"/>
+      <c r="W7" s="21"/>
+      <c r="X7" s="21"/>
+      <c r="Y7" s="21"/>
+      <c r="Z7" s="21"/>
     </row>
     <row r="8" ht="60.0" customHeight="1">
-      <c r="A8" s="19">
+      <c r="A8" s="21">
         <v>7.0</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="19"/>
-      <c r="Z8" s="19"/>
+      <c r="B8" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="21"/>
+      <c r="U8" s="21"/>
+      <c r="V8" s="21"/>
+      <c r="W8" s="21"/>
+      <c r="X8" s="21"/>
+      <c r="Y8" s="21"/>
+      <c r="Z8" s="21"/>
     </row>
     <row r="9" ht="60.0" customHeight="1">
-      <c r="A9" s="15">
+      <c r="A9" s="10">
         <v>8.0</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E9" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
+      <c r="B9" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="21"/>
+      <c r="U9" s="21"/>
+      <c r="V9" s="21"/>
+      <c r="W9" s="21"/>
+      <c r="X9" s="21"/>
+      <c r="Y9" s="21"/>
+      <c r="Z9" s="21"/>
     </row>
     <row r="10" ht="60.0" customHeight="1">
-      <c r="A10" s="15">
+      <c r="A10" s="10">
         <v>9.0</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="E10" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>145</v>
+      <c r="B10" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="11" ht="60.0" customHeight="1">
-      <c r="A11" s="15">
+      <c r="A11" s="10">
         <v>10.0</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>156</v>
+      <c r="B11" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="12" ht="60.0" customHeight="1">
-      <c r="A12" s="28">
+      <c r="A12" s="35">
         <v>11.0</v>
       </c>
-      <c r="B12" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="E12" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>164</v>
+      <c r="B12" s="35" t="s">
+        <v>207</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="35" t="s">
+        <v>211</v>
+      </c>
+      <c r="F12" s="35" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="13" ht="60.0" customHeight="1">
-      <c r="A13" s="28">
+      <c r="A13" s="35">
         <v>12.0</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>170</v>
+      <c r="B13" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="E13" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="F13" s="35" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="14" ht="60.0" customHeight="1">
-      <c r="A14" s="28">
+      <c r="A14" s="35">
         <v>13.0</v>
       </c>
-      <c r="B14" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="C14" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="F14" s="28" t="s">
-        <v>175</v>
+      <c r="B14" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>229</v>
+      </c>
+      <c r="E14" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="F14" s="35" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="15" ht="60.0" customHeight="1">
-      <c r="A15" s="28">
+      <c r="A15" s="35">
         <v>14.0</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="C15" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="D15" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E15" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="F15" s="28" t="s">
-        <v>183</v>
+      <c r="B15" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="D15" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="F15" s="35" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="16" ht="60.0" customHeight="1">
-      <c r="A16" s="28">
+      <c r="A16" s="35">
         <v>15.0</v>
       </c>
-      <c r="B16" s="28" t="s">
-        <v>186</v>
-      </c>
-      <c r="C16" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>189</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>191</v>
+      <c r="B16" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="D16" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="E16" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="F16" s="35" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="17" ht="60.0" customHeight="1">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
     </row>
     <row r="18" ht="60.0" customHeight="1">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
     </row>
     <row r="19" ht="60.0" customHeight="1">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
     </row>
     <row r="20" ht="60.0" customHeight="1">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
     </row>
     <row r="21" ht="60.0" customHeight="1">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
     </row>
     <row r="22" ht="60.0" customHeight="1">
-      <c r="A22" s="15"/>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
     </row>
     <row r="23" ht="60.0" customHeight="1">
-      <c r="A23" s="15"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
     </row>
     <row r="24" ht="60.0" customHeight="1">
-      <c r="A24" s="15"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
     </row>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1"/>
@@ -4704,74 +4777,74 @@
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>205</v>
+      <c r="A30" s="4" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>211</v>
+      <c r="A31" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>215</v>
+      <c r="A32" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>219</v>
+      <c r="A33" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>222</v>
+      <c r="A34" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>225</v>
+      <c r="A35" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>228</v>
+      <c r="A36" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1"/>
@@ -5766,236 +5839,274 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
+      <c r="A4" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>27</v>
+      <c r="A5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="14"/>
+      <c r="A6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="14"/>
+      <c r="A7" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" s="14" t="s">
+      <c r="A8" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="18" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="14"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="14"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="14"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="14"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="14"/>
+      <c r="B15" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D16" s="14"/>
+      <c r="A16" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="14"/>
+      <c r="A17" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="14"/>
+      <c r="A18" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="s">
-        <v>115</v>
+      <c r="A20" s="29" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="21" t="s">
-        <v>118</v>
+      <c r="A21" s="30" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="21" t="s">
-        <v>120</v>
+      <c r="A22" s="30" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
-        <v>124</v>
+      <c r="A25" s="4" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="22" t="s">
-        <v>126</v>
+      <c r="A26" s="31" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="25" t="s">
-        <v>132</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>135</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>139</v>
+      <c r="A27" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="26" t="s">
+      <c r="A28" s="34">
+        <v>1.0</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="D29" s="34" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
+      <c r="B30" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="31" ht="15.75" customHeight="1"/>
     <row r="32" ht="15.75" customHeight="1"/>
